--- a/Black-White-Unit-Auto Tests.xlsx
+++ b/Black-White-Unit-Auto Tests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://w2shared-my.sharepoint.com/personal/dave_sushames01_student_wandw_ac_nz/Documents/Documents/Testing and Secure Coding/GroupAssignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="125" documentId="13_ncr:1_{2ECF283D-0ABF-464E-9B99-68B1B0E591C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6ED84C98-57E0-49C9-84A8-AE6C27100654}"/>
+  <xr:revisionPtr revIDLastSave="134" documentId="13_ncr:1_{2ECF283D-0ABF-464E-9B99-68B1B0E591C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5AED62C1-BE3E-460D-9275-AC15FA3D088C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{84DD0BDD-34A0-4121-B413-A041E4D23E14}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2098" uniqueCount="1108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2098" uniqueCount="1107">
   <si>
     <t>Black Box Testing</t>
   </si>
@@ -2457,9 +2457,6 @@
     <t>Statement</t>
   </si>
   <si>
-    <t xml:space="preserve">Statemnet and Branch </t>
-  </si>
-  <si>
     <t xml:space="preserve">Statement and Branch </t>
   </si>
   <si>
@@ -3529,7 +3526,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4446,7 +4443,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7054E7F-35B4-4301-A3E0-05785D130094}">
   <dimension ref="A1:I84"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.85546875" style="2" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" style="2" bestFit="1" customWidth="1"/>
@@ -4460,7 +4457,7 @@
     <col min="10" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="15.75" thickBot="1">
       <c r="A1" s="9"/>
       <c r="B1" s="38" t="s">
         <v>0</v>
@@ -4473,7 +4470,7 @@
       <c r="H1" s="38"/>
       <c r="I1" s="38"/>
     </row>
-    <row r="2" spans="1:9" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="31.5" thickTop="1" thickBot="1">
       <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
@@ -4502,7 +4499,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="49.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="49.5" customHeight="1" thickTop="1">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -4529,7 +4526,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="30">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
@@ -4556,7 +4553,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="30">
       <c r="A5" s="1" t="s">
         <v>23</v>
       </c>
@@ -4585,7 +4582,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="60">
       <c r="A6" s="1" t="s">
         <v>30</v>
       </c>
@@ -4614,7 +4611,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="75">
       <c r="A7" s="1" t="s">
         <v>34</v>
       </c>
@@ -4643,7 +4640,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="75">
       <c r="A8" s="1" t="s">
         <v>38</v>
       </c>
@@ -4672,7 +4669,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="75">
       <c r="A9" s="1" t="s">
         <v>42</v>
       </c>
@@ -4701,7 +4698,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="30">
       <c r="A10" s="1" t="s">
         <v>46</v>
       </c>
@@ -4730,7 +4727,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="31.5" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>50</v>
       </c>
@@ -4759,7 +4756,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="29.25" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>55</v>
       </c>
@@ -4788,7 +4785,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="28.5" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>59</v>
       </c>
@@ -4817,7 +4814,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="34.5" customHeight="1">
       <c r="A14" s="7" t="s">
         <v>63</v>
       </c>
@@ -4846,7 +4843,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="37.5" customHeight="1">
       <c r="A15" s="7" t="s">
         <v>64</v>
       </c>
@@ -4875,7 +4872,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="30">
       <c r="A16" s="7" t="s">
         <v>66</v>
       </c>
@@ -4902,7 +4899,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="30">
       <c r="A17" s="7" t="s">
         <v>72</v>
       </c>
@@ -4929,7 +4926,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="30">
       <c r="A18" s="7" t="s">
         <v>77</v>
       </c>
@@ -4956,7 +4953,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="30">
       <c r="A19" s="7" t="s">
         <v>82</v>
       </c>
@@ -4983,7 +4980,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="30">
       <c r="A20" s="7" t="s">
         <v>85</v>
       </c>
@@ -5010,7 +5007,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="30">
       <c r="A21" s="7" t="s">
         <v>90</v>
       </c>
@@ -5037,7 +5034,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="30">
       <c r="A22" s="7" t="s">
         <v>92</v>
       </c>
@@ -5064,7 +5061,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="30">
       <c r="A23" s="7" t="s">
         <v>97</v>
       </c>
@@ -5091,7 +5088,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="30">
       <c r="A24" s="7" t="s">
         <v>99</v>
       </c>
@@ -5118,7 +5115,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="30">
       <c r="A25" s="7" t="s">
         <v>105</v>
       </c>
@@ -5145,7 +5142,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="30">
       <c r="A26" s="7" t="s">
         <v>110</v>
       </c>
@@ -5172,7 +5169,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="30">
       <c r="A27" s="7" t="s">
         <v>115</v>
       </c>
@@ -5199,7 +5196,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="45">
       <c r="A28" s="7" t="s">
         <v>120</v>
       </c>
@@ -5226,7 +5223,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="29.25" customHeight="1">
       <c r="A29" s="7" t="s">
         <v>125</v>
       </c>
@@ -5253,7 +5250,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="30">
       <c r="A30" s="7" t="s">
         <v>131</v>
       </c>
@@ -5280,7 +5277,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="30">
       <c r="A31" s="7" t="s">
         <v>135</v>
       </c>
@@ -5307,7 +5304,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="30">
       <c r="A32" s="7" t="s">
         <v>139</v>
       </c>
@@ -5334,7 +5331,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" ht="45">
       <c r="A33" s="7" t="s">
         <v>143</v>
       </c>
@@ -5361,7 +5358,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" ht="30">
       <c r="A34" s="7" t="s">
         <v>146</v>
       </c>
@@ -5388,7 +5385,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" ht="30">
       <c r="A35" s="7" t="s">
         <v>152</v>
       </c>
@@ -5415,7 +5412,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" ht="30">
       <c r="A36" s="7" t="s">
         <v>156</v>
       </c>
@@ -5442,7 +5439,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" ht="30">
       <c r="A37" s="7" t="s">
         <v>160</v>
       </c>
@@ -5469,7 +5466,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" ht="45">
       <c r="A38" s="7" t="s">
         <v>164</v>
       </c>
@@ -5496,12 +5493,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" ht="30">
       <c r="A39" s="7" t="s">
         <v>167</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>12</v>
@@ -5510,22 +5507,22 @@
         <v>101</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>755</v>
       </c>
       <c r="G39" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="H39" s="1" t="s">
         <v>774</v>
       </c>
-      <c r="H39" s="1" t="s">
-        <v>775</v>
-      </c>
       <c r="I39" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" ht="31.5" customHeight="1">
       <c r="A40" s="7" t="s">
         <v>172</v>
       </c>
@@ -5552,7 +5549,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" ht="30">
       <c r="A41" s="7" t="s">
         <v>177</v>
       </c>
@@ -5579,12 +5576,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" ht="30">
       <c r="A42" s="7" t="s">
         <v>181</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>12</v>
@@ -5593,22 +5590,22 @@
         <v>127</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>755</v>
       </c>
       <c r="G42" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="H42" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="H42" s="1" t="s">
-        <v>772</v>
-      </c>
       <c r="I42" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" ht="30">
       <c r="A43" s="7" t="s">
         <v>185</v>
       </c>
@@ -5635,7 +5632,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" ht="30">
       <c r="A44" s="7" t="s">
         <v>189</v>
       </c>
@@ -5662,12 +5659,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" ht="45">
       <c r="A45" s="7" t="s">
         <v>193</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>12</v>
@@ -5676,22 +5673,22 @@
         <v>148</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>755</v>
       </c>
       <c r="G45" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="H45" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="H45" s="1" t="s">
-        <v>764</v>
-      </c>
       <c r="I45" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" ht="30">
       <c r="A46" s="7" t="s">
         <v>200</v>
       </c>
@@ -5718,7 +5715,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" ht="30">
       <c r="A47" s="7" t="s">
         <v>204</v>
       </c>
@@ -5745,7 +5742,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" ht="75">
       <c r="A48" s="7" t="s">
         <v>208</v>
       </c>
@@ -5774,7 +5771,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" ht="75">
       <c r="A49" s="7" t="s">
         <v>213</v>
       </c>
@@ -5803,7 +5800,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" ht="75">
       <c r="A50" s="7" t="s">
         <v>215</v>
       </c>
@@ -5832,7 +5829,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" ht="75">
       <c r="A51" s="7" t="s">
         <v>219</v>
       </c>
@@ -5861,7 +5858,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" ht="75">
       <c r="A52" s="7" t="s">
         <v>222</v>
       </c>
@@ -5890,7 +5887,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" ht="60">
       <c r="A53" s="7" t="s">
         <v>227</v>
       </c>
@@ -5919,7 +5916,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" ht="30">
       <c r="A54" s="7" t="s">
         <v>231</v>
       </c>
@@ -5946,7 +5943,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" ht="30">
       <c r="A55" s="7" t="s">
         <v>235</v>
       </c>
@@ -5973,7 +5970,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" ht="45">
       <c r="A56" s="7" t="s">
         <v>239</v>
       </c>
@@ -6002,7 +5999,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" ht="60">
       <c r="A57" s="7" t="s">
         <v>242</v>
       </c>
@@ -6031,7 +6028,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" ht="45">
       <c r="A58" s="7" t="s">
         <v>243</v>
       </c>
@@ -6060,7 +6057,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" ht="45">
       <c r="A59" s="9" t="s">
         <v>246</v>
       </c>
@@ -6089,7 +6086,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" ht="60">
       <c r="A60" s="9" t="s">
         <v>248</v>
       </c>
@@ -6118,7 +6115,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" ht="45">
       <c r="A61" s="9" t="s">
         <v>253</v>
       </c>
@@ -6147,7 +6144,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" ht="30">
       <c r="A62" s="9" t="s">
         <v>257</v>
       </c>
@@ -6174,7 +6171,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" ht="30">
       <c r="A63" s="9" t="s">
         <v>260</v>
       </c>
@@ -6201,7 +6198,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" ht="60">
       <c r="A64" s="9" t="s">
         <v>262</v>
       </c>
@@ -6230,7 +6227,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" ht="60">
       <c r="A65" s="9" t="s">
         <v>266</v>
       </c>
@@ -6259,7 +6256,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" ht="75">
       <c r="A66" s="9" t="s">
         <v>269</v>
       </c>
@@ -6288,7 +6285,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" ht="75">
       <c r="A67" s="9" t="s">
         <v>270</v>
       </c>
@@ -6317,7 +6314,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" ht="60">
       <c r="A68" s="9" t="s">
         <v>271</v>
       </c>
@@ -6346,7 +6343,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" ht="60">
       <c r="A69" s="9" t="s">
         <v>274</v>
       </c>
@@ -6375,7 +6372,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" ht="75">
       <c r="A70" s="9" t="s">
         <v>275</v>
       </c>
@@ -6404,7 +6401,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" ht="75">
       <c r="A71" s="9" t="s">
         <v>278</v>
       </c>
@@ -6433,7 +6430,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" ht="30">
       <c r="A72" s="9" t="s">
         <v>284</v>
       </c>
@@ -6460,7 +6457,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" ht="30">
       <c r="A73" s="9" t="s">
         <v>285</v>
       </c>
@@ -6487,7 +6484,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" ht="30">
       <c r="A74" s="9" t="s">
         <v>286</v>
       </c>
@@ -6514,7 +6511,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9">
       <c r="A75" s="9"/>
       <c r="B75" s="9"/>
       <c r="C75" s="9"/>
@@ -6525,10 +6522,10 @@
       <c r="H75" s="9"/>
       <c r="I75" s="9"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9">
       <c r="A76" s="9"/>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9">
       <c r="A77" s="9"/>
       <c r="B77" s="9"/>
       <c r="C77" s="9"/>
@@ -6539,7 +6536,7 @@
       <c r="H77" s="9"/>
       <c r="I77" s="9"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9">
       <c r="A78" s="9"/>
       <c r="B78" s="9"/>
       <c r="C78" s="9"/>
@@ -6550,7 +6547,7 @@
       <c r="H78" s="9"/>
       <c r="I78" s="9"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9">
       <c r="A79" s="9"/>
       <c r="B79" s="9"/>
       <c r="C79" s="9"/>
@@ -6561,7 +6558,7 @@
       <c r="H79" s="9"/>
       <c r="I79" s="9"/>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9">
       <c r="A80" s="9"/>
       <c r="B80" s="9"/>
       <c r="C80" s="9"/>
@@ -6572,7 +6569,7 @@
       <c r="H80" s="9"/>
       <c r="I80" s="9"/>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9">
       <c r="A81" s="9"/>
       <c r="B81" s="9"/>
       <c r="C81" s="9"/>
@@ -6583,7 +6580,7 @@
       <c r="H81" s="9"/>
       <c r="I81" s="9"/>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9">
       <c r="A82" s="9"/>
       <c r="B82" s="9"/>
       <c r="C82" s="9"/>
@@ -6594,7 +6591,7 @@
       <c r="H82" s="9"/>
       <c r="I82" s="9"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9">
       <c r="B83" s="9"/>
       <c r="C83" s="9"/>
       <c r="D83" s="9"/>
@@ -6604,7 +6601,7 @@
       <c r="H83" s="9"/>
       <c r="I83" s="9"/>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9">
       <c r="B84" s="9"/>
       <c r="C84" s="9"/>
       <c r="D84" s="9"/>
@@ -6627,20 +6624,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34913591-753E-4C12-8F06-CC3CB8FC123F}">
   <dimension ref="A1:H125"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="26.7109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="35.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="31.7109375" style="2" customWidth="1"/>
     <col min="3" max="3" width="19.7109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="43.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="36.28515625" style="2" customWidth="1"/>
     <col min="5" max="5" width="56.140625" style="2" customWidth="1"/>
     <col min="6" max="6" width="47.5703125" style="2" customWidth="1"/>
     <col min="7" max="7" width="39.5703125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="29.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.85546875" style="2" customWidth="1"/>
     <col min="9" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="19.5" thickBot="1">
       <c r="B1" s="39" t="s">
         <v>287</v>
       </c>
@@ -6651,7 +6648,7 @@
       <c r="G1" s="39"/>
       <c r="H1" s="39"/>
     </row>
-    <row r="2" spans="1:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="16.5" thickTop="1" thickBot="1">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
@@ -6677,7 +6674,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="51" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="51" customHeight="1" thickTop="1">
       <c r="A3" s="24" t="s">
         <v>291</v>
       </c>
@@ -6703,7 +6700,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="45.75" customHeight="1">
       <c r="A4" s="24" t="s">
         <v>292</v>
       </c>
@@ -6729,7 +6726,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="63.75" customHeight="1">
       <c r="A5" s="24" t="s">
         <v>293</v>
       </c>
@@ -6755,7 +6752,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="93.75" customHeight="1">
       <c r="A6" s="24" t="s">
         <v>294</v>
       </c>
@@ -6781,7 +6778,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="89.25" customHeight="1">
       <c r="A7" s="24" t="s">
         <v>295</v>
       </c>
@@ -6807,7 +6804,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="45">
       <c r="A8" s="24" t="s">
         <v>296</v>
       </c>
@@ -6833,7 +6830,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="30">
       <c r="A9" s="24" t="s">
         <v>297</v>
       </c>
@@ -6859,7 +6856,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8">
       <c r="A10" s="24" t="s">
         <v>384</v>
       </c>
@@ -6885,7 +6882,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="30">
       <c r="A11" s="24" t="s">
         <v>298</v>
       </c>
@@ -6911,7 +6908,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="45">
       <c r="A12" s="24" t="s">
         <v>299</v>
       </c>
@@ -6937,7 +6934,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="30">
       <c r="A13" s="24" t="s">
         <v>300</v>
       </c>
@@ -6963,7 +6960,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="30">
       <c r="A14" s="24" t="s">
         <v>301</v>
       </c>
@@ -6989,7 +6986,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="30">
       <c r="A15" s="24" t="s">
         <v>302</v>
       </c>
@@ -7012,10 +7009,10 @@
         <v>406</v>
       </c>
       <c r="H15" s="22" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="30">
       <c r="A16" s="24" t="s">
         <v>303</v>
       </c>
@@ -7041,7 +7038,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="30">
       <c r="A17" s="24" t="s">
         <v>304</v>
       </c>
@@ -7064,10 +7061,10 @@
         <v>415</v>
       </c>
       <c r="H17" s="22" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="30">
       <c r="A18" s="24" t="s">
         <v>305</v>
       </c>
@@ -7093,7 +7090,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="30">
       <c r="A19" s="24" t="s">
         <v>306</v>
       </c>
@@ -7119,7 +7116,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="30">
       <c r="A20" s="24" t="s">
         <v>307</v>
       </c>
@@ -7145,7 +7142,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="30">
       <c r="A21" s="24" t="s">
         <v>308</v>
       </c>
@@ -7171,7 +7168,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8">
       <c r="A22" s="24" t="s">
         <v>309</v>
       </c>
@@ -7197,7 +7194,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8">
       <c r="A23" s="24" t="s">
         <v>310</v>
       </c>
@@ -7223,7 +7220,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8">
       <c r="A24" s="24" t="s">
         <v>311</v>
       </c>
@@ -7249,7 +7246,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8">
       <c r="A25" s="24" t="s">
         <v>312</v>
       </c>
@@ -7275,7 +7272,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8">
       <c r="A26" s="24" t="s">
         <v>313</v>
       </c>
@@ -7301,7 +7298,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="30">
       <c r="A27" s="24" t="s">
         <v>314</v>
       </c>
@@ -7327,7 +7324,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="30">
       <c r="A28" s="24" t="s">
         <v>315</v>
       </c>
@@ -7353,7 +7350,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="30">
       <c r="A29" s="24" t="s">
         <v>316</v>
       </c>
@@ -7379,7 +7376,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="75">
       <c r="A30" s="24" t="s">
         <v>317</v>
       </c>
@@ -7405,7 +7402,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="45">
       <c r="A31" s="24" t="s">
         <v>318</v>
       </c>
@@ -7428,10 +7425,10 @@
         <v>464</v>
       </c>
       <c r="H31" s="22" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" s="24" t="s">
         <v>319</v>
       </c>
@@ -7457,7 +7454,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8">
       <c r="A33" s="24" t="s">
         <v>320</v>
       </c>
@@ -7483,7 +7480,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8">
       <c r="A34" s="24" t="s">
         <v>321</v>
       </c>
@@ -7509,7 +7506,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="30">
       <c r="A35" s="24" t="s">
         <v>322</v>
       </c>
@@ -7532,10 +7529,10 @@
         <v>478</v>
       </c>
       <c r="H35" s="22" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="30">
       <c r="A36" s="24" t="s">
         <v>479</v>
       </c>
@@ -7558,10 +7555,10 @@
         <v>483</v>
       </c>
       <c r="H36" s="22" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="45">
       <c r="A37" s="24" t="s">
         <v>484</v>
       </c>
@@ -7587,7 +7584,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="30">
       <c r="A38" s="24" t="s">
         <v>489</v>
       </c>
@@ -7613,7 +7610,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="30">
       <c r="A39" s="24" t="s">
         <v>494</v>
       </c>
@@ -7636,10 +7633,10 @@
         <v>497</v>
       </c>
       <c r="H39" s="22" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="30">
       <c r="A40" s="24" t="s">
         <v>498</v>
       </c>
@@ -7665,7 +7662,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="30">
       <c r="A41" s="24" t="s">
         <v>502</v>
       </c>
@@ -7691,7 +7688,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="30">
       <c r="A42" s="24" t="s">
         <v>505</v>
       </c>
@@ -7714,10 +7711,10 @@
         <v>508</v>
       </c>
       <c r="H42" s="22" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
       <c r="A43" s="24" t="s">
         <v>509</v>
       </c>
@@ -7743,7 +7740,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8">
       <c r="A44" s="24" t="s">
         <v>514</v>
       </c>
@@ -7769,7 +7766,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8">
       <c r="A45" s="24" t="s">
         <v>517</v>
       </c>
@@ -7795,7 +7792,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8">
       <c r="A46" s="24" t="s">
         <v>521</v>
       </c>
@@ -7818,10 +7815,10 @@
         <v>525</v>
       </c>
       <c r="H46" s="22" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
       <c r="A47" s="24" t="s">
         <v>526</v>
       </c>
@@ -7847,7 +7844,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8">
       <c r="A48" s="24" t="s">
         <v>532</v>
       </c>
@@ -7873,7 +7870,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8">
       <c r="A49" s="24" t="s">
         <v>535</v>
       </c>
@@ -7899,7 +7896,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="30">
       <c r="A50" s="24" t="s">
         <v>538</v>
       </c>
@@ -7925,7 +7922,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="45">
       <c r="A51" s="24" t="s">
         <v>542</v>
       </c>
@@ -7951,7 +7948,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="30">
       <c r="A52" s="24" t="s">
         <v>547</v>
       </c>
@@ -7977,7 +7974,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8">
       <c r="A53" s="24" t="s">
         <v>552</v>
       </c>
@@ -8003,7 +8000,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8">
       <c r="A54" s="24" t="s">
         <v>557</v>
       </c>
@@ -8029,7 +8026,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8">
       <c r="A55" s="26" t="s">
         <v>560</v>
       </c>
@@ -8055,7 +8052,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="30">
       <c r="A56" s="24" t="s">
         <v>565</v>
       </c>
@@ -8081,7 +8078,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="30">
       <c r="A57" s="28" t="s">
         <v>569</v>
       </c>
@@ -8107,7 +8104,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="30">
       <c r="A58" s="24" t="s">
         <v>575</v>
       </c>
@@ -8133,7 +8130,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="45">
       <c r="A59" s="24" t="s">
         <v>579</v>
       </c>
@@ -8156,10 +8153,10 @@
         <v>582</v>
       </c>
       <c r="H59" s="29" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
       <c r="A60" s="24" t="s">
         <v>583</v>
       </c>
@@ -8185,7 +8182,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8">
       <c r="A61" s="24" t="s">
         <v>586</v>
       </c>
@@ -8211,7 +8208,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="30">
       <c r="A62" s="24" t="s">
         <v>589</v>
       </c>
@@ -8237,7 +8234,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="30">
       <c r="A63" s="24" t="s">
         <v>592</v>
       </c>
@@ -8263,7 +8260,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8">
       <c r="A64" s="24" t="s">
         <v>597</v>
       </c>
@@ -8289,7 +8286,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" ht="30">
       <c r="A65" s="24" t="s">
         <v>601</v>
       </c>
@@ -8312,10 +8309,10 @@
         <v>578</v>
       </c>
       <c r="H65" s="29" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
       <c r="A66" s="24" t="s">
         <v>605</v>
       </c>
@@ -8341,7 +8338,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8">
       <c r="A67" s="24" t="s">
         <v>608</v>
       </c>
@@ -8367,7 +8364,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8">
       <c r="A68" s="24" t="s">
         <v>611</v>
       </c>
@@ -8393,7 +8390,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8">
       <c r="A69" s="24" t="s">
         <v>615</v>
       </c>
@@ -8416,10 +8413,10 @@
         <v>618</v>
       </c>
       <c r="H69" s="29" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
       <c r="A70" s="24" t="s">
         <v>619</v>
       </c>
@@ -8445,7 +8442,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" ht="30">
       <c r="A71" s="24" t="s">
         <v>624</v>
       </c>
@@ -8471,7 +8468,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" ht="30">
       <c r="A72" s="24" t="s">
         <v>628</v>
       </c>
@@ -8497,7 +8494,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8">
       <c r="A73" s="24" t="s">
         <v>632</v>
       </c>
@@ -8523,7 +8520,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8">
       <c r="A74" s="24" t="s">
         <v>636</v>
       </c>
@@ -8549,7 +8546,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8">
       <c r="A75" s="24" t="s">
         <v>639</v>
       </c>
@@ -8575,7 +8572,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8">
       <c r="A76" s="24" t="s">
         <v>641</v>
       </c>
@@ -8601,7 +8598,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8">
       <c r="A77" s="24" t="s">
         <v>644</v>
       </c>
@@ -8627,7 +8624,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8">
       <c r="A78" s="24" t="s">
         <v>647</v>
       </c>
@@ -8653,7 +8650,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8">
       <c r="A79" s="24" t="s">
         <v>651</v>
       </c>
@@ -8679,7 +8676,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" ht="45">
       <c r="A80" s="24" t="s">
         <v>653</v>
       </c>
@@ -8705,7 +8702,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" ht="30">
       <c r="A81" s="24" t="s">
         <v>658</v>
       </c>
@@ -8728,10 +8725,10 @@
         <v>661</v>
       </c>
       <c r="H81" s="23" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
       <c r="A82" s="24" t="s">
         <v>662</v>
       </c>
@@ -8757,7 +8754,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8">
       <c r="A83" s="24" t="s">
         <v>664</v>
       </c>
@@ -8783,7 +8780,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8">
       <c r="A84" s="24" t="s">
         <v>666</v>
       </c>
@@ -8809,7 +8806,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" ht="45">
       <c r="A85" s="24" t="s">
         <v>669</v>
       </c>
@@ -8835,7 +8832,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" ht="30">
       <c r="A86" s="24" t="s">
         <v>674</v>
       </c>
@@ -8858,10 +8855,10 @@
         <v>676</v>
       </c>
       <c r="H86" s="23" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
       <c r="A87" s="24" t="s">
         <v>677</v>
       </c>
@@ -8887,7 +8884,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8">
       <c r="A88" s="24" t="s">
         <v>679</v>
       </c>
@@ -8910,10 +8907,10 @@
         <v>439</v>
       </c>
       <c r="H88" s="23" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
       <c r="A89" s="24" t="s">
         <v>681</v>
       </c>
@@ -8939,7 +8936,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8">
       <c r="A90" s="24" t="s">
         <v>684</v>
       </c>
@@ -8962,10 +8959,10 @@
         <v>618</v>
       </c>
       <c r="H90" s="23" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
       <c r="A91" s="24" t="s">
         <v>685</v>
       </c>
@@ -8991,7 +8988,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8">
       <c r="A92" s="24" t="s">
         <v>691</v>
       </c>
@@ -9017,7 +9014,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" ht="30">
       <c r="A93" s="24" t="s">
         <v>696</v>
       </c>
@@ -9043,7 +9040,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8">
       <c r="A94" s="24" t="s">
         <v>701</v>
       </c>
@@ -9069,7 +9066,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8">
       <c r="A95" s="24" t="s">
         <v>707</v>
       </c>
@@ -9095,7 +9092,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8">
       <c r="A96" s="24" t="s">
         <v>711</v>
       </c>
@@ -9121,7 +9118,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8">
       <c r="A97" s="13"/>
       <c r="B97" s="13"/>
       <c r="C97" s="13"/>
@@ -9130,7 +9127,7 @@
       <c r="F97" s="13"/>
       <c r="G97" s="13"/>
     </row>
-    <row r="98" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" ht="45">
       <c r="A98" s="31" t="s">
         <v>715</v>
       </c>
@@ -9147,16 +9144,16 @@
         <v>718</v>
       </c>
       <c r="F98" s="31" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="G98" s="31" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H98" s="32" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" ht="60">
       <c r="A99" s="31" t="s">
         <v>719</v>
       </c>
@@ -9179,10 +9176,10 @@
         <v>375</v>
       </c>
       <c r="H99" s="32" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" ht="60">
       <c r="A100" s="31" t="s">
         <v>722</v>
       </c>
@@ -9205,10 +9202,10 @@
         <v>375</v>
       </c>
       <c r="H100" s="32" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" ht="60">
       <c r="A101" s="31" t="s">
         <v>725</v>
       </c>
@@ -9231,10 +9228,10 @@
         <v>375</v>
       </c>
       <c r="H101" s="32" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" ht="60">
       <c r="A102" s="31" t="s">
         <v>728</v>
       </c>
@@ -9257,10 +9254,10 @@
         <v>375</v>
       </c>
       <c r="H102" s="32" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" ht="60">
       <c r="A103" s="31" t="s">
         <v>731</v>
       </c>
@@ -9283,10 +9280,10 @@
         <v>375</v>
       </c>
       <c r="H103" s="32" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" ht="30">
       <c r="A104" s="31" t="s">
         <v>734</v>
       </c>
@@ -9303,16 +9300,16 @@
         <v>736</v>
       </c>
       <c r="F104" s="31" t="s">
+        <v>776</v>
+      </c>
+      <c r="G104" s="31" t="s">
         <v>777</v>
       </c>
-      <c r="G104" s="31" t="s">
-        <v>778</v>
-      </c>
       <c r="H104" s="32" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
       <c r="A105" s="12"/>
       <c r="B105" s="12"/>
       <c r="C105" s="12"/>
@@ -9321,7 +9318,7 @@
       <c r="F105" s="13"/>
       <c r="G105" s="13"/>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8">
       <c r="A106" s="12"/>
       <c r="B106" s="12"/>
       <c r="C106" s="12"/>
@@ -9330,7 +9327,7 @@
       <c r="F106" s="13"/>
       <c r="G106" s="13"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8">
       <c r="A107" s="12"/>
       <c r="B107" s="12"/>
       <c r="C107" s="12"/>
@@ -9339,7 +9336,7 @@
       <c r="F107" s="13"/>
       <c r="G107" s="13"/>
     </row>
-    <row r="108" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" ht="45">
       <c r="A108" s="31" t="s">
         <v>737</v>
       </c>
@@ -9356,16 +9353,16 @@
         <v>741</v>
       </c>
       <c r="F108" s="34" t="s">
+        <v>780</v>
+      </c>
+      <c r="G108" s="35" t="s">
         <v>781</v>
       </c>
-      <c r="G108" s="35" t="s">
-        <v>782</v>
-      </c>
       <c r="H108" s="32" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
       <c r="A109" s="31" t="s">
         <v>742</v>
       </c>
@@ -9382,16 +9379,16 @@
         <v>745</v>
       </c>
       <c r="F109" s="35" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="G109" s="35" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H109" s="32" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
       <c r="A110" s="13"/>
       <c r="B110" s="13"/>
       <c r="C110" s="13"/>
@@ -9400,7 +9397,7 @@
       <c r="F110" s="13"/>
       <c r="G110" s="13"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8">
       <c r="A111" s="12"/>
       <c r="B111" s="12"/>
       <c r="C111" s="12"/>
@@ -9417,7 +9414,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8">
       <c r="A112" s="12"/>
       <c r="B112" s="12"/>
       <c r="C112" s="12"/>
@@ -9434,7 +9431,7 @@
         <v>0.35899999999999999</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7">
       <c r="A113" s="12"/>
       <c r="B113" s="12"/>
       <c r="C113" s="12"/>
@@ -9451,7 +9448,7 @@
         <v>0.71799999999999997</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7">
       <c r="A114" s="12"/>
       <c r="B114" s="12"/>
       <c r="C114" s="12"/>
@@ -9468,7 +9465,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7">
       <c r="A115" s="12"/>
       <c r="B115" s="12"/>
       <c r="C115" s="12"/>
@@ -9477,7 +9474,7 @@
       <c r="F115" s="12"/>
       <c r="G115" s="12"/>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7">
       <c r="A116" s="12"/>
       <c r="B116" s="12"/>
       <c r="C116" s="12"/>
@@ -9486,7 +9483,7 @@
       <c r="F116" s="12"/>
       <c r="G116" s="12"/>
     </row>
-    <row r="117" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" ht="75">
       <c r="A117" s="14" t="s">
         <v>327</v>
       </c>
@@ -9503,7 +9500,7 @@
       <c r="F117" s="12"/>
       <c r="G117" s="12"/>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7">
       <c r="A118" s="19" t="s">
         <v>747</v>
       </c>
@@ -9520,7 +9517,7 @@
       <c r="F118" s="12"/>
       <c r="G118" s="12"/>
     </row>
-    <row r="119" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" ht="90">
       <c r="A119" s="19" t="s">
         <v>331</v>
       </c>
@@ -9537,7 +9534,7 @@
       <c r="F119" s="12"/>
       <c r="G119" s="12"/>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7">
       <c r="A120" s="19" t="s">
         <v>747</v>
       </c>
@@ -9554,7 +9551,7 @@
       <c r="F120" s="12"/>
       <c r="G120" s="12"/>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7">
       <c r="A121" s="40" t="s">
         <v>333</v>
       </c>
@@ -9573,7 +9570,7 @@
       <c r="F121" s="45"/>
       <c r="G121" s="45"/>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7">
       <c r="A122" s="40"/>
       <c r="B122" s="42"/>
       <c r="C122" s="42"/>
@@ -9584,7 +9581,7 @@
       <c r="F122" s="45"/>
       <c r="G122" s="45"/>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7">
       <c r="A123" s="40"/>
       <c r="B123" s="42"/>
       <c r="C123" s="42"/>
@@ -9595,7 +9592,7 @@
       <c r="F123" s="45"/>
       <c r="G123" s="45"/>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7">
       <c r="A124" s="40"/>
       <c r="B124" s="42"/>
       <c r="C124" s="42"/>
@@ -9606,7 +9603,7 @@
       <c r="F124" s="45"/>
       <c r="G124" s="45"/>
     </row>
-    <row r="125" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" ht="30">
       <c r="A125" s="41"/>
       <c r="B125" s="43"/>
       <c r="C125" s="43"/>
@@ -9636,7 +9633,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FAABC76-6758-4DE5-9192-7D2F0BD08C03}">
   <dimension ref="A1:F102"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="81.140625" customWidth="1"/>
@@ -9647,7 +9644,7 @@
     <col min="7" max="7" width="12.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21.75" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="21.75" thickTop="1">
       <c r="A1" s="37" t="s">
         <v>335</v>
       </c>
@@ -9667,1178 +9664,1178 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="16.5" customHeight="1">
       <c r="A2" s="36" t="s">
         <v>338</v>
       </c>
       <c r="B2" s="36" t="s">
+        <v>852</v>
+      </c>
+      <c r="C2" s="36" t="s">
+        <v>783</v>
+      </c>
+      <c r="D2" s="36" t="s">
         <v>853</v>
       </c>
-      <c r="C2" s="36" t="s">
-        <v>784</v>
-      </c>
-      <c r="D2" s="36" t="s">
+      <c r="E2" s="36" t="s">
         <v>854</v>
       </c>
-      <c r="E2" s="36" t="s">
-        <v>855</v>
-      </c>
       <c r="F2" s="36" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3" s="36" t="s">
         <v>339</v>
       </c>
       <c r="B3" s="36" t="s">
+        <v>855</v>
+      </c>
+      <c r="C3" s="36" t="s">
+        <v>783</v>
+      </c>
+      <c r="D3" s="36" t="s">
         <v>856</v>
       </c>
-      <c r="C3" s="36" t="s">
-        <v>784</v>
-      </c>
-      <c r="D3" s="36" t="s">
-        <v>857</v>
-      </c>
       <c r="E3" s="36" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="F3" s="36" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4" s="36" t="s">
         <v>340</v>
       </c>
       <c r="B4" s="36" t="s">
+        <v>857</v>
+      </c>
+      <c r="C4" s="36" t="s">
+        <v>783</v>
+      </c>
+      <c r="D4" s="36" t="s">
         <v>858</v>
       </c>
-      <c r="C4" s="36" t="s">
-        <v>784</v>
-      </c>
-      <c r="D4" s="36" t="s">
+      <c r="E4" s="36" t="s">
         <v>859</v>
       </c>
-      <c r="E4" s="36" t="s">
-        <v>860</v>
-      </c>
       <c r="F4" s="36" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5" s="36" t="s">
         <v>341</v>
       </c>
       <c r="B5" s="36" t="s">
+        <v>860</v>
+      </c>
+      <c r="C5" s="36" t="s">
+        <v>783</v>
+      </c>
+      <c r="D5" s="36" t="s">
+        <v>858</v>
+      </c>
+      <c r="E5" s="36" t="s">
         <v>861</v>
       </c>
-      <c r="C5" s="36" t="s">
-        <v>784</v>
-      </c>
-      <c r="D5" s="36" t="s">
-        <v>859</v>
-      </c>
-      <c r="E5" s="36" t="s">
-        <v>862</v>
-      </c>
       <c r="F5" s="36" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6" s="36" t="s">
         <v>342</v>
       </c>
       <c r="B6" s="36" t="s">
+        <v>862</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>783</v>
+      </c>
+      <c r="D6" s="36" t="s">
+        <v>858</v>
+      </c>
+      <c r="E6" s="36" t="s">
         <v>863</v>
       </c>
-      <c r="C6" s="36" t="s">
-        <v>784</v>
-      </c>
-      <c r="D6" s="36" t="s">
-        <v>859</v>
-      </c>
-      <c r="E6" s="36" t="s">
-        <v>864</v>
-      </c>
       <c r="F6" s="36" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="16.5">
       <c r="A7" s="36" t="s">
         <v>343</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="C7" s="36" t="s">
+        <v>783</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E7" s="36" t="s">
         <v>784</v>
       </c>
-      <c r="D7" s="36" t="s">
-        <v>1090</v>
-      </c>
-      <c r="E7" s="36" t="s">
-        <v>785</v>
-      </c>
       <c r="F7" s="36" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8" s="36" t="s">
         <v>344</v>
       </c>
       <c r="B8" s="36" t="s">
+        <v>865</v>
+      </c>
+      <c r="C8" s="36" t="s">
+        <v>785</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>786</v>
+      </c>
+      <c r="E8" s="36" t="s">
         <v>866</v>
       </c>
-      <c r="C8" s="36" t="s">
-        <v>786</v>
-      </c>
-      <c r="D8" s="36" t="s">
-        <v>787</v>
-      </c>
-      <c r="E8" s="36" t="s">
-        <v>867</v>
-      </c>
       <c r="F8" s="36" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9" s="36" t="s">
         <v>345</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="D9" s="36" t="s">
+        <v>867</v>
+      </c>
+      <c r="E9" s="36" t="s">
         <v>868</v>
       </c>
-      <c r="E9" s="36" t="s">
-        <v>869</v>
-      </c>
       <c r="F9" s="36" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10" s="36" t="s">
         <v>346</v>
       </c>
       <c r="B10" s="36" t="s">
+        <v>869</v>
+      </c>
+      <c r="C10" s="36" t="s">
+        <v>785</v>
+      </c>
+      <c r="D10" s="36" t="s">
         <v>870</v>
       </c>
-      <c r="C10" s="36" t="s">
-        <v>786</v>
-      </c>
-      <c r="D10" s="36" t="s">
+      <c r="E10" s="36" t="s">
         <v>871</v>
       </c>
-      <c r="E10" s="36" t="s">
-        <v>872</v>
-      </c>
       <c r="F10" s="36" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="17.25" customHeight="1">
       <c r="A11" s="36" t="s">
         <v>347</v>
       </c>
       <c r="B11" s="36" t="s">
+        <v>872</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>785</v>
+      </c>
+      <c r="D11" s="36" t="s">
         <v>873</v>
       </c>
-      <c r="C11" s="36" t="s">
-        <v>786</v>
-      </c>
-      <c r="D11" s="36" t="s">
+      <c r="E11" s="36" t="s">
         <v>874</v>
       </c>
-      <c r="E11" s="36" t="s">
-        <v>875</v>
-      </c>
       <c r="F11" s="36" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="18.75" customHeight="1">
       <c r="A12" s="36" t="s">
         <v>348</v>
       </c>
       <c r="B12" s="36" t="s">
+        <v>875</v>
+      </c>
+      <c r="C12" s="36" t="s">
+        <v>785</v>
+      </c>
+      <c r="D12" s="36" t="s">
         <v>876</v>
       </c>
-      <c r="C12" s="36" t="s">
-        <v>786</v>
-      </c>
-      <c r="D12" s="36" t="s">
+      <c r="E12" s="36" t="s">
         <v>877</v>
       </c>
-      <c r="E12" s="36" t="s">
-        <v>878</v>
-      </c>
       <c r="F12" s="36" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="17.25" customHeight="1">
       <c r="A13" s="36" t="s">
         <v>349</v>
       </c>
       <c r="B13" s="36" t="s">
+        <v>878</v>
+      </c>
+      <c r="C13" s="36" t="s">
+        <v>785</v>
+      </c>
+      <c r="D13" s="36" t="s">
         <v>879</v>
       </c>
-      <c r="C13" s="36" t="s">
-        <v>786</v>
-      </c>
-      <c r="D13" s="36" t="s">
+      <c r="E13" s="36" t="s">
         <v>880</v>
       </c>
-      <c r="E13" s="36" t="s">
-        <v>881</v>
-      </c>
       <c r="F13" s="36" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="17.25" customHeight="1">
       <c r="A14" s="36" t="s">
         <v>350</v>
       </c>
       <c r="B14" s="36" t="s">
+        <v>881</v>
+      </c>
+      <c r="C14" s="36" t="s">
+        <v>785</v>
+      </c>
+      <c r="D14" s="36" t="s">
         <v>882</v>
       </c>
-      <c r="C14" s="36" t="s">
-        <v>786</v>
-      </c>
-      <c r="D14" s="36" t="s">
+      <c r="E14" s="36" t="s">
         <v>883</v>
       </c>
-      <c r="E14" s="36" t="s">
-        <v>884</v>
-      </c>
       <c r="F14" s="36" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="17.25" customHeight="1">
       <c r="A15" s="36" t="s">
         <v>351</v>
       </c>
       <c r="B15" s="36" t="s">
+        <v>884</v>
+      </c>
+      <c r="C15" s="36" t="s">
+        <v>785</v>
+      </c>
+      <c r="D15" s="36" t="s">
         <v>885</v>
       </c>
-      <c r="C15" s="36" t="s">
-        <v>786</v>
-      </c>
-      <c r="D15" s="36" t="s">
+      <c r="E15" s="36" t="s">
         <v>886</v>
       </c>
-      <c r="E15" s="36" t="s">
-        <v>887</v>
-      </c>
       <c r="F15" s="36" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="17.25" customHeight="1">
       <c r="A16" s="36" t="s">
         <v>352</v>
       </c>
       <c r="B16" s="36" t="s">
+        <v>887</v>
+      </c>
+      <c r="C16" s="36" t="s">
+        <v>785</v>
+      </c>
+      <c r="D16" s="36" t="s">
         <v>888</v>
       </c>
-      <c r="C16" s="36" t="s">
-        <v>786</v>
-      </c>
-      <c r="D16" s="36" t="s">
+      <c r="E16" s="36" t="s">
         <v>889</v>
       </c>
-      <c r="E16" s="36" t="s">
-        <v>890</v>
-      </c>
       <c r="F16" s="36" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="17.25" customHeight="1">
       <c r="A17" s="36" t="s">
         <v>353</v>
       </c>
       <c r="B17" s="36" t="s">
+        <v>890</v>
+      </c>
+      <c r="C17" s="36" t="s">
+        <v>785</v>
+      </c>
+      <c r="D17" s="36" t="s">
         <v>891</v>
       </c>
-      <c r="C17" s="36" t="s">
-        <v>786</v>
-      </c>
-      <c r="D17" s="36" t="s">
+      <c r="E17" s="36" t="s">
         <v>892</v>
       </c>
-      <c r="E17" s="36" t="s">
-        <v>893</v>
-      </c>
       <c r="F17" s="36" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="17.25" customHeight="1">
       <c r="A18" s="36" t="s">
         <v>354</v>
       </c>
       <c r="B18" s="36" t="s">
+        <v>893</v>
+      </c>
+      <c r="C18" s="36" t="s">
+        <v>785</v>
+      </c>
+      <c r="D18" s="36" t="s">
         <v>894</v>
       </c>
-      <c r="C18" s="36" t="s">
-        <v>786</v>
-      </c>
-      <c r="D18" s="36" t="s">
-        <v>895</v>
-      </c>
       <c r="E18" s="36" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="F18" s="36" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="17.25" customHeight="1">
       <c r="A19" s="36" t="s">
         <v>355</v>
       </c>
       <c r="B19" s="36" t="s">
+        <v>895</v>
+      </c>
+      <c r="C19" s="36" t="s">
+        <v>785</v>
+      </c>
+      <c r="D19" s="36" t="s">
         <v>896</v>
       </c>
-      <c r="C19" s="36" t="s">
+      <c r="E19" s="36" t="s">
+        <v>816</v>
+      </c>
+      <c r="F19" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="36" t="s">
+        <v>788</v>
+      </c>
+      <c r="B20" s="36" t="s">
+        <v>897</v>
+      </c>
+      <c r="C20" s="36" t="s">
+        <v>785</v>
+      </c>
+      <c r="D20" s="36" t="s">
+        <v>898</v>
+      </c>
+      <c r="E20" s="36" t="s">
+        <v>899</v>
+      </c>
+      <c r="F20" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="20.25" customHeight="1">
+      <c r="A21" s="36" t="s">
+        <v>789</v>
+      </c>
+      <c r="B21" s="36" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C21" s="36" t="s">
+        <v>785</v>
+      </c>
+      <c r="D21" s="36" t="s">
+        <v>900</v>
+      </c>
+      <c r="E21" s="36" t="s">
+        <v>901</v>
+      </c>
+      <c r="F21" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="36" t="s">
+        <v>790</v>
+      </c>
+      <c r="B22" s="36" t="s">
+        <v>902</v>
+      </c>
+      <c r="C22" s="36" t="s">
+        <v>785</v>
+      </c>
+      <c r="D22" s="36" t="s">
+        <v>903</v>
+      </c>
+      <c r="E22" s="36" t="s">
+        <v>904</v>
+      </c>
+      <c r="F22" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="36" t="s">
+        <v>791</v>
+      </c>
+      <c r="B23" s="36" t="s">
+        <v>905</v>
+      </c>
+      <c r="C23" s="36" t="s">
+        <v>785</v>
+      </c>
+      <c r="D23" s="36" t="s">
+        <v>888</v>
+      </c>
+      <c r="E23" s="36" t="s">
+        <v>906</v>
+      </c>
+      <c r="F23" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="36" t="s">
+        <v>792</v>
+      </c>
+      <c r="B24" s="36" t="s">
+        <v>907</v>
+      </c>
+      <c r="C24" s="36" t="s">
+        <v>785</v>
+      </c>
+      <c r="D24" s="36" t="s">
+        <v>908</v>
+      </c>
+      <c r="E24" s="36" t="s">
+        <v>909</v>
+      </c>
+      <c r="F24" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="36" t="s">
+        <v>793</v>
+      </c>
+      <c r="B25" s="36" t="s">
+        <v>910</v>
+      </c>
+      <c r="C25" s="36" t="s">
+        <v>785</v>
+      </c>
+      <c r="D25" s="36" t="s">
+        <v>911</v>
+      </c>
+      <c r="E25" s="36" t="s">
+        <v>892</v>
+      </c>
+      <c r="F25" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="36" t="s">
+        <v>794</v>
+      </c>
+      <c r="B26" s="36" t="s">
+        <v>912</v>
+      </c>
+      <c r="C26" s="36" t="s">
+        <v>785</v>
+      </c>
+      <c r="D26" s="36" t="s">
+        <v>888</v>
+      </c>
+      <c r="E26" s="36" t="s">
+        <v>906</v>
+      </c>
+      <c r="F26" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="36" t="s">
+        <v>795</v>
+      </c>
+      <c r="B27" s="36" t="s">
+        <v>913</v>
+      </c>
+      <c r="C27" s="36" t="s">
+        <v>785</v>
+      </c>
+      <c r="D27" s="36" t="s">
+        <v>888</v>
+      </c>
+      <c r="E27" s="36" t="s">
+        <v>914</v>
+      </c>
+      <c r="F27" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="36" t="s">
+        <v>796</v>
+      </c>
+      <c r="B28" s="36" t="s">
+        <v>915</v>
+      </c>
+      <c r="C28" s="36" t="s">
+        <v>785</v>
+      </c>
+      <c r="D28" s="36" t="s">
+        <v>894</v>
+      </c>
+      <c r="E28" s="36" t="s">
+        <v>916</v>
+      </c>
+      <c r="F28" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="36" t="s">
+        <v>797</v>
+      </c>
+      <c r="B29" s="36" t="s">
+        <v>917</v>
+      </c>
+      <c r="C29" s="36" t="s">
+        <v>785</v>
+      </c>
+      <c r="D29" s="36" t="s">
+        <v>888</v>
+      </c>
+      <c r="E29" s="36" t="s">
+        <v>798</v>
+      </c>
+      <c r="F29" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="36" t="s">
+        <v>799</v>
+      </c>
+      <c r="B30" s="36" t="s">
+        <v>918</v>
+      </c>
+      <c r="C30" s="36" t="s">
+        <v>785</v>
+      </c>
+      <c r="D30" s="36" t="s">
+        <v>894</v>
+      </c>
+      <c r="E30" s="36" t="s">
+        <v>800</v>
+      </c>
+      <c r="F30" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="36" t="s">
+        <v>801</v>
+      </c>
+      <c r="B31" s="36" t="s">
+        <v>919</v>
+      </c>
+      <c r="C31" s="36" t="s">
+        <v>785</v>
+      </c>
+      <c r="D31" s="36" t="s">
+        <v>920</v>
+      </c>
+      <c r="E31" s="36" t="s">
+        <v>798</v>
+      </c>
+      <c r="F31" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="36" t="s">
+        <v>802</v>
+      </c>
+      <c r="B32" s="36" t="s">
+        <v>921</v>
+      </c>
+      <c r="C32" s="36" t="s">
+        <v>785</v>
+      </c>
+      <c r="D32" s="36" t="s">
+        <v>922</v>
+      </c>
+      <c r="E32" s="36" t="s">
+        <v>800</v>
+      </c>
+      <c r="F32" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="36" t="s">
+        <v>803</v>
+      </c>
+      <c r="B33" s="36" t="s">
+        <v>923</v>
+      </c>
+      <c r="C33" s="36" t="s">
+        <v>804</v>
+      </c>
+      <c r="D33" s="36" t="s">
         <v>786</v>
       </c>
-      <c r="D19" s="36" t="s">
-        <v>897</v>
-      </c>
-      <c r="E19" s="36" t="s">
+      <c r="E33" s="36" t="s">
+        <v>924</v>
+      </c>
+      <c r="F33" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="36" t="s">
+        <v>805</v>
+      </c>
+      <c r="B34" s="36" t="s">
+        <v>925</v>
+      </c>
+      <c r="C34" s="36" t="s">
+        <v>804</v>
+      </c>
+      <c r="D34" s="36" t="s">
+        <v>870</v>
+      </c>
+      <c r="E34" s="36" t="s">
+        <v>926</v>
+      </c>
+      <c r="F34" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="36" t="s">
+        <v>806</v>
+      </c>
+      <c r="B35" s="36" t="s">
+        <v>927</v>
+      </c>
+      <c r="C35" s="36" t="s">
+        <v>804</v>
+      </c>
+      <c r="D35" s="36" t="s">
+        <v>928</v>
+      </c>
+      <c r="E35" s="36" t="s">
+        <v>929</v>
+      </c>
+      <c r="F35" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="36" t="s">
+        <v>807</v>
+      </c>
+      <c r="B36" s="36" t="s">
+        <v>930</v>
+      </c>
+      <c r="C36" s="36" t="s">
+        <v>804</v>
+      </c>
+      <c r="D36" s="36" t="s">
+        <v>931</v>
+      </c>
+      <c r="E36" s="36" t="s">
+        <v>932</v>
+      </c>
+      <c r="F36" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="36" t="s">
+        <v>808</v>
+      </c>
+      <c r="B37" s="36" t="s">
+        <v>933</v>
+      </c>
+      <c r="C37" s="36" t="s">
+        <v>804</v>
+      </c>
+      <c r="D37" s="36" t="s">
+        <v>882</v>
+      </c>
+      <c r="E37" s="36" t="s">
+        <v>934</v>
+      </c>
+      <c r="F37" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="36" t="s">
+        <v>809</v>
+      </c>
+      <c r="B38" s="36" t="s">
+        <v>935</v>
+      </c>
+      <c r="C38" s="36" t="s">
+        <v>804</v>
+      </c>
+      <c r="D38" s="36" t="s">
+        <v>885</v>
+      </c>
+      <c r="E38" s="36" t="s">
+        <v>936</v>
+      </c>
+      <c r="F38" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="36" t="s">
+        <v>810</v>
+      </c>
+      <c r="B39" s="36" t="s">
+        <v>937</v>
+      </c>
+      <c r="C39" s="36" t="s">
+        <v>804</v>
+      </c>
+      <c r="D39" s="36" t="s">
+        <v>786</v>
+      </c>
+      <c r="E39" s="36" t="s">
+        <v>934</v>
+      </c>
+      <c r="F39" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="36" t="s">
+        <v>811</v>
+      </c>
+      <c r="B40" s="36" t="s">
+        <v>938</v>
+      </c>
+      <c r="C40" s="36" t="s">
+        <v>804</v>
+      </c>
+      <c r="D40" s="36" t="s">
+        <v>939</v>
+      </c>
+      <c r="E40" s="36" t="s">
+        <v>932</v>
+      </c>
+      <c r="F40" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="36" t="s">
+        <v>812</v>
+      </c>
+      <c r="B41" s="36" t="s">
+        <v>940</v>
+      </c>
+      <c r="C41" s="36" t="s">
+        <v>804</v>
+      </c>
+      <c r="D41" s="36" t="s">
+        <v>888</v>
+      </c>
+      <c r="E41" s="36" t="s">
+        <v>941</v>
+      </c>
+      <c r="F41" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="36" t="s">
+        <v>813</v>
+      </c>
+      <c r="B42" s="36" t="s">
+        <v>890</v>
+      </c>
+      <c r="C42" s="36" t="s">
+        <v>804</v>
+      </c>
+      <c r="D42" s="36" t="s">
+        <v>891</v>
+      </c>
+      <c r="E42" s="36" t="s">
+        <v>892</v>
+      </c>
+      <c r="F42" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="36" t="s">
+        <v>814</v>
+      </c>
+      <c r="B43" s="36" t="s">
+        <v>893</v>
+      </c>
+      <c r="C43" s="36" t="s">
+        <v>804</v>
+      </c>
+      <c r="D43" s="36" t="s">
+        <v>894</v>
+      </c>
+      <c r="E43" s="36" t="s">
+        <v>892</v>
+      </c>
+      <c r="F43" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="36" t="s">
+        <v>815</v>
+      </c>
+      <c r="B44" s="36" t="s">
+        <v>895</v>
+      </c>
+      <c r="C44" s="36" t="s">
+        <v>804</v>
+      </c>
+      <c r="D44" s="36" t="s">
+        <v>896</v>
+      </c>
+      <c r="E44" s="36" t="s">
+        <v>816</v>
+      </c>
+      <c r="F44" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="36" t="s">
         <v>817</v>
       </c>
-      <c r="F19" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="36" t="s">
-        <v>789</v>
-      </c>
-      <c r="B20" s="36" t="s">
-        <v>898</v>
-      </c>
-      <c r="C20" s="36" t="s">
-        <v>786</v>
-      </c>
-      <c r="D20" s="36" t="s">
-        <v>899</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>900</v>
-      </c>
-      <c r="F20" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="36" t="s">
-        <v>790</v>
-      </c>
-      <c r="B21" s="36" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C21" s="36" t="s">
-        <v>786</v>
-      </c>
-      <c r="D21" s="36" t="s">
-        <v>901</v>
-      </c>
-      <c r="E21" s="36" t="s">
+      <c r="B45" s="36" t="s">
+        <v>942</v>
+      </c>
+      <c r="C45" s="36" t="s">
+        <v>804</v>
+      </c>
+      <c r="D45" s="36" t="s">
+        <v>943</v>
+      </c>
+      <c r="E45" s="36" t="s">
+        <v>944</v>
+      </c>
+      <c r="F45" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="36" t="s">
+        <v>818</v>
+      </c>
+      <c r="B46" s="36" t="s">
         <v>902</v>
       </c>
-      <c r="F21" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="36" t="s">
-        <v>791</v>
-      </c>
-      <c r="B22" s="36" t="s">
-        <v>903</v>
-      </c>
-      <c r="C22" s="36" t="s">
-        <v>786</v>
-      </c>
-      <c r="D22" s="36" t="s">
+      <c r="C46" s="36" t="s">
+        <v>804</v>
+      </c>
+      <c r="D46" s="36" t="s">
+        <v>945</v>
+      </c>
+      <c r="E46" s="36" t="s">
         <v>904</v>
       </c>
-      <c r="E22" s="36" t="s">
-        <v>905</v>
-      </c>
-      <c r="F22" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="36" t="s">
-        <v>792</v>
-      </c>
-      <c r="B23" s="36" t="s">
-        <v>906</v>
-      </c>
-      <c r="C23" s="36" t="s">
-        <v>786</v>
-      </c>
-      <c r="D23" s="36" t="s">
-        <v>889</v>
-      </c>
-      <c r="E23" s="36" t="s">
-        <v>907</v>
-      </c>
-      <c r="F23" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="36" t="s">
-        <v>793</v>
-      </c>
-      <c r="B24" s="36" t="s">
-        <v>908</v>
-      </c>
-      <c r="C24" s="36" t="s">
-        <v>786</v>
-      </c>
-      <c r="D24" s="36" t="s">
-        <v>909</v>
-      </c>
-      <c r="E24" s="36" t="s">
-        <v>910</v>
-      </c>
-      <c r="F24" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="36" t="s">
-        <v>794</v>
-      </c>
-      <c r="B25" s="36" t="s">
-        <v>911</v>
-      </c>
-      <c r="C25" s="36" t="s">
-        <v>786</v>
-      </c>
-      <c r="D25" s="36" t="s">
-        <v>912</v>
-      </c>
-      <c r="E25" s="36" t="s">
-        <v>893</v>
-      </c>
-      <c r="F25" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="36" t="s">
-        <v>795</v>
-      </c>
-      <c r="B26" s="36" t="s">
-        <v>913</v>
-      </c>
-      <c r="C26" s="36" t="s">
-        <v>786</v>
-      </c>
-      <c r="D26" s="36" t="s">
-        <v>889</v>
-      </c>
-      <c r="E26" s="36" t="s">
-        <v>907</v>
-      </c>
-      <c r="F26" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="36" t="s">
-        <v>796</v>
-      </c>
-      <c r="B27" s="36" t="s">
-        <v>914</v>
-      </c>
-      <c r="C27" s="36" t="s">
-        <v>786</v>
-      </c>
-      <c r="D27" s="36" t="s">
-        <v>889</v>
-      </c>
-      <c r="E27" s="36" t="s">
+      <c r="F46" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="36" t="s">
+        <v>819</v>
+      </c>
+      <c r="B47" s="36" t="s">
+        <v>946</v>
+      </c>
+      <c r="C47" s="36" t="s">
+        <v>804</v>
+      </c>
+      <c r="D47" s="36" t="s">
+        <v>947</v>
+      </c>
+      <c r="E47" s="36" t="s">
+        <v>948</v>
+      </c>
+      <c r="F47" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="36" t="s">
+        <v>820</v>
+      </c>
+      <c r="B48" s="36" t="s">
+        <v>949</v>
+      </c>
+      <c r="C48" s="36" t="s">
+        <v>804</v>
+      </c>
+      <c r="D48" s="36" t="s">
+        <v>888</v>
+      </c>
+      <c r="E48" s="36" t="s">
+        <v>941</v>
+      </c>
+      <c r="F48" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="36" t="s">
+        <v>821</v>
+      </c>
+      <c r="B49" s="36" t="s">
+        <v>950</v>
+      </c>
+      <c r="C49" s="36" t="s">
+        <v>804</v>
+      </c>
+      <c r="D49" s="36" t="s">
+        <v>894</v>
+      </c>
+      <c r="E49" s="36" t="s">
+        <v>892</v>
+      </c>
+      <c r="F49" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="36" t="s">
+        <v>822</v>
+      </c>
+      <c r="B50" s="36" t="s">
+        <v>951</v>
+      </c>
+      <c r="C50" s="36" t="s">
+        <v>804</v>
+      </c>
+      <c r="D50" s="36" t="s">
+        <v>891</v>
+      </c>
+      <c r="E50" s="36" t="s">
+        <v>892</v>
+      </c>
+      <c r="F50" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="36" t="s">
+        <v>823</v>
+      </c>
+      <c r="B51" s="36" t="s">
+        <v>952</v>
+      </c>
+      <c r="C51" s="36" t="s">
+        <v>804</v>
+      </c>
+      <c r="D51" s="36" t="s">
+        <v>953</v>
+      </c>
+      <c r="E51" s="36" t="s">
+        <v>954</v>
+      </c>
+      <c r="F51" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="36" t="s">
+        <v>824</v>
+      </c>
+      <c r="B52" s="36" t="s">
+        <v>955</v>
+      </c>
+      <c r="C52" s="36" t="s">
+        <v>804</v>
+      </c>
+      <c r="D52" s="36" t="s">
+        <v>956</v>
+      </c>
+      <c r="E52" s="36" t="s">
+        <v>892</v>
+      </c>
+      <c r="F52" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="36" t="s">
+        <v>825</v>
+      </c>
+      <c r="B53" s="36" t="s">
+        <v>957</v>
+      </c>
+      <c r="C53" s="36" t="s">
+        <v>804</v>
+      </c>
+      <c r="D53" s="36" t="s">
+        <v>945</v>
+      </c>
+      <c r="E53" s="36" t="s">
+        <v>904</v>
+      </c>
+      <c r="F53" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="36" t="s">
+        <v>826</v>
+      </c>
+      <c r="B54" s="36" t="s">
+        <v>958</v>
+      </c>
+      <c r="C54" s="36" t="s">
+        <v>804</v>
+      </c>
+      <c r="D54" s="36" t="s">
+        <v>888</v>
+      </c>
+      <c r="E54" s="36" t="s">
+        <v>941</v>
+      </c>
+      <c r="F54" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="36" t="s">
+        <v>827</v>
+      </c>
+      <c r="B55" s="36" t="s">
+        <v>959</v>
+      </c>
+      <c r="C55" s="36" t="s">
+        <v>804</v>
+      </c>
+      <c r="D55" s="36" t="s">
+        <v>894</v>
+      </c>
+      <c r="E55" s="36" t="s">
+        <v>892</v>
+      </c>
+      <c r="F55" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="36" t="s">
+        <v>828</v>
+      </c>
+      <c r="B56" s="36" t="s">
+        <v>960</v>
+      </c>
+      <c r="C56" s="36" t="s">
+        <v>804</v>
+      </c>
+      <c r="D56" s="36" t="s">
+        <v>888</v>
+      </c>
+      <c r="E56" s="36" t="s">
+        <v>961</v>
+      </c>
+      <c r="F56" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="36" t="s">
+        <v>829</v>
+      </c>
+      <c r="B57" s="36" t="s">
         <v>915</v>
       </c>
-      <c r="F27" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="36" t="s">
-        <v>797</v>
-      </c>
-      <c r="B28" s="36" t="s">
+      <c r="C57" s="36" t="s">
+        <v>804</v>
+      </c>
+      <c r="D57" s="36" t="s">
+        <v>894</v>
+      </c>
+      <c r="E57" s="36" t="s">
         <v>916</v>
       </c>
-      <c r="C28" s="36" t="s">
-        <v>786</v>
-      </c>
-      <c r="D28" s="36" t="s">
-        <v>895</v>
-      </c>
-      <c r="E28" s="36" t="s">
-        <v>917</v>
-      </c>
-      <c r="F28" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="36" t="s">
+      <c r="F57" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" s="36" t="s">
+        <v>830</v>
+      </c>
+      <c r="B58" s="36" t="s">
+        <v>962</v>
+      </c>
+      <c r="C58" s="36" t="s">
+        <v>804</v>
+      </c>
+      <c r="D58" s="36" t="s">
+        <v>888</v>
+      </c>
+      <c r="E58" s="36" t="s">
         <v>798</v>
       </c>
-      <c r="B29" s="36" t="s">
-        <v>918</v>
-      </c>
-      <c r="C29" s="36" t="s">
-        <v>786</v>
-      </c>
-      <c r="D29" s="36" t="s">
-        <v>889</v>
-      </c>
-      <c r="E29" s="36" t="s">
-        <v>799</v>
-      </c>
-      <c r="F29" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="36" t="s">
+      <c r="F58" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" s="36" t="s">
+        <v>831</v>
+      </c>
+      <c r="B59" s="36" t="s">
+        <v>963</v>
+      </c>
+      <c r="C59" s="36" t="s">
+        <v>804</v>
+      </c>
+      <c r="D59" s="36" t="s">
+        <v>894</v>
+      </c>
+      <c r="E59" s="36" t="s">
         <v>800</v>
       </c>
-      <c r="B30" s="36" t="s">
-        <v>919</v>
-      </c>
-      <c r="C30" s="36" t="s">
-        <v>786</v>
-      </c>
-      <c r="D30" s="36" t="s">
-        <v>895</v>
-      </c>
-      <c r="E30" s="36" t="s">
-        <v>801</v>
-      </c>
-      <c r="F30" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="36" t="s">
-        <v>802</v>
-      </c>
-      <c r="B31" s="36" t="s">
-        <v>920</v>
-      </c>
-      <c r="C31" s="36" t="s">
-        <v>786</v>
-      </c>
-      <c r="D31" s="36" t="s">
-        <v>921</v>
-      </c>
-      <c r="E31" s="36" t="s">
-        <v>799</v>
-      </c>
-      <c r="F31" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="36" t="s">
-        <v>803</v>
-      </c>
-      <c r="B32" s="36" t="s">
-        <v>922</v>
-      </c>
-      <c r="C32" s="36" t="s">
-        <v>786</v>
-      </c>
-      <c r="D32" s="36" t="s">
-        <v>923</v>
-      </c>
-      <c r="E32" s="36" t="s">
-        <v>801</v>
-      </c>
-      <c r="F32" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="36" t="s">
-        <v>804</v>
-      </c>
-      <c r="B33" s="36" t="s">
-        <v>924</v>
-      </c>
-      <c r="C33" s="36" t="s">
-        <v>805</v>
-      </c>
-      <c r="D33" s="36" t="s">
-        <v>787</v>
-      </c>
-      <c r="E33" s="36" t="s">
-        <v>925</v>
-      </c>
-      <c r="F33" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="36" t="s">
-        <v>806</v>
-      </c>
-      <c r="B34" s="36" t="s">
-        <v>926</v>
-      </c>
-      <c r="C34" s="36" t="s">
-        <v>805</v>
-      </c>
-      <c r="D34" s="36" t="s">
-        <v>871</v>
-      </c>
-      <c r="E34" s="36" t="s">
-        <v>927</v>
-      </c>
-      <c r="F34" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="36" t="s">
-        <v>807</v>
-      </c>
-      <c r="B35" s="36" t="s">
-        <v>928</v>
-      </c>
-      <c r="C35" s="36" t="s">
-        <v>805</v>
-      </c>
-      <c r="D35" s="36" t="s">
-        <v>929</v>
-      </c>
-      <c r="E35" s="36" t="s">
-        <v>930</v>
-      </c>
-      <c r="F35" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="36" t="s">
-        <v>808</v>
-      </c>
-      <c r="B36" s="36" t="s">
-        <v>931</v>
-      </c>
-      <c r="C36" s="36" t="s">
-        <v>805</v>
-      </c>
-      <c r="D36" s="36" t="s">
-        <v>932</v>
-      </c>
-      <c r="E36" s="36" t="s">
-        <v>933</v>
-      </c>
-      <c r="F36" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="36" t="s">
-        <v>809</v>
-      </c>
-      <c r="B37" s="36" t="s">
-        <v>934</v>
-      </c>
-      <c r="C37" s="36" t="s">
-        <v>805</v>
-      </c>
-      <c r="D37" s="36" t="s">
-        <v>883</v>
-      </c>
-      <c r="E37" s="36" t="s">
-        <v>935</v>
-      </c>
-      <c r="F37" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="36" t="s">
-        <v>810</v>
-      </c>
-      <c r="B38" s="36" t="s">
-        <v>936</v>
-      </c>
-      <c r="C38" s="36" t="s">
-        <v>805</v>
-      </c>
-      <c r="D38" s="36" t="s">
-        <v>886</v>
-      </c>
-      <c r="E38" s="36" t="s">
-        <v>937</v>
-      </c>
-      <c r="F38" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="36" t="s">
-        <v>811</v>
-      </c>
-      <c r="B39" s="36" t="s">
-        <v>938</v>
-      </c>
-      <c r="C39" s="36" t="s">
-        <v>805</v>
-      </c>
-      <c r="D39" s="36" t="s">
-        <v>787</v>
-      </c>
-      <c r="E39" s="36" t="s">
-        <v>935</v>
-      </c>
-      <c r="F39" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="36" t="s">
-        <v>812</v>
-      </c>
-      <c r="B40" s="36" t="s">
-        <v>939</v>
-      </c>
-      <c r="C40" s="36" t="s">
-        <v>805</v>
-      </c>
-      <c r="D40" s="36" t="s">
-        <v>940</v>
-      </c>
-      <c r="E40" s="36" t="s">
-        <v>933</v>
-      </c>
-      <c r="F40" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="36" t="s">
-        <v>813</v>
-      </c>
-      <c r="B41" s="36" t="s">
-        <v>941</v>
-      </c>
-      <c r="C41" s="36" t="s">
-        <v>805</v>
-      </c>
-      <c r="D41" s="36" t="s">
-        <v>889</v>
-      </c>
-      <c r="E41" s="36" t="s">
-        <v>942</v>
-      </c>
-      <c r="F41" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="36" t="s">
-        <v>814</v>
-      </c>
-      <c r="B42" s="36" t="s">
-        <v>891</v>
-      </c>
-      <c r="C42" s="36" t="s">
-        <v>805</v>
-      </c>
-      <c r="D42" s="36" t="s">
-        <v>892</v>
-      </c>
-      <c r="E42" s="36" t="s">
-        <v>893</v>
-      </c>
-      <c r="F42" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="36" t="s">
-        <v>815</v>
-      </c>
-      <c r="B43" s="36" t="s">
-        <v>894</v>
-      </c>
-      <c r="C43" s="36" t="s">
-        <v>805</v>
-      </c>
-      <c r="D43" s="36" t="s">
-        <v>895</v>
-      </c>
-      <c r="E43" s="36" t="s">
-        <v>893</v>
-      </c>
-      <c r="F43" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="36" t="s">
-        <v>816</v>
-      </c>
-      <c r="B44" s="36" t="s">
-        <v>896</v>
-      </c>
-      <c r="C44" s="36" t="s">
-        <v>805</v>
-      </c>
-      <c r="D44" s="36" t="s">
-        <v>897</v>
-      </c>
-      <c r="E44" s="36" t="s">
-        <v>817</v>
-      </c>
-      <c r="F44" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="36" t="s">
-        <v>818</v>
-      </c>
-      <c r="B45" s="36" t="s">
-        <v>943</v>
-      </c>
-      <c r="C45" s="36" t="s">
-        <v>805</v>
-      </c>
-      <c r="D45" s="36" t="s">
-        <v>944</v>
-      </c>
-      <c r="E45" s="36" t="s">
-        <v>945</v>
-      </c>
-      <c r="F45" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="36" t="s">
-        <v>819</v>
-      </c>
-      <c r="B46" s="36" t="s">
-        <v>903</v>
-      </c>
-      <c r="C46" s="36" t="s">
-        <v>805</v>
-      </c>
-      <c r="D46" s="36" t="s">
-        <v>946</v>
-      </c>
-      <c r="E46" s="36" t="s">
-        <v>905</v>
-      </c>
-      <c r="F46" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="36" t="s">
-        <v>820</v>
-      </c>
-      <c r="B47" s="36" t="s">
-        <v>947</v>
-      </c>
-      <c r="C47" s="36" t="s">
-        <v>805</v>
-      </c>
-      <c r="D47" s="36" t="s">
-        <v>948</v>
-      </c>
-      <c r="E47" s="36" t="s">
-        <v>949</v>
-      </c>
-      <c r="F47" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="36" t="s">
-        <v>821</v>
-      </c>
-      <c r="B48" s="36" t="s">
-        <v>950</v>
-      </c>
-      <c r="C48" s="36" t="s">
-        <v>805</v>
-      </c>
-      <c r="D48" s="36" t="s">
-        <v>889</v>
-      </c>
-      <c r="E48" s="36" t="s">
-        <v>942</v>
-      </c>
-      <c r="F48" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="36" t="s">
-        <v>822</v>
-      </c>
-      <c r="B49" s="36" t="s">
-        <v>951</v>
-      </c>
-      <c r="C49" s="36" t="s">
-        <v>805</v>
-      </c>
-      <c r="D49" s="36" t="s">
-        <v>895</v>
-      </c>
-      <c r="E49" s="36" t="s">
-        <v>893</v>
-      </c>
-      <c r="F49" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="36" t="s">
-        <v>823</v>
-      </c>
-      <c r="B50" s="36" t="s">
-        <v>952</v>
-      </c>
-      <c r="C50" s="36" t="s">
-        <v>805</v>
-      </c>
-      <c r="D50" s="36" t="s">
-        <v>892</v>
-      </c>
-      <c r="E50" s="36" t="s">
-        <v>893</v>
-      </c>
-      <c r="F50" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="36" t="s">
-        <v>824</v>
-      </c>
-      <c r="B51" s="36" t="s">
-        <v>953</v>
-      </c>
-      <c r="C51" s="36" t="s">
-        <v>805</v>
-      </c>
-      <c r="D51" s="36" t="s">
-        <v>954</v>
-      </c>
-      <c r="E51" s="36" t="s">
-        <v>955</v>
-      </c>
-      <c r="F51" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="36" t="s">
-        <v>825</v>
-      </c>
-      <c r="B52" s="36" t="s">
-        <v>956</v>
-      </c>
-      <c r="C52" s="36" t="s">
-        <v>805</v>
-      </c>
-      <c r="D52" s="36" t="s">
-        <v>957</v>
-      </c>
-      <c r="E52" s="36" t="s">
-        <v>893</v>
-      </c>
-      <c r="F52" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="36" t="s">
-        <v>826</v>
-      </c>
-      <c r="B53" s="36" t="s">
-        <v>958</v>
-      </c>
-      <c r="C53" s="36" t="s">
-        <v>805</v>
-      </c>
-      <c r="D53" s="36" t="s">
-        <v>946</v>
-      </c>
-      <c r="E53" s="36" t="s">
-        <v>905</v>
-      </c>
-      <c r="F53" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="36" t="s">
-        <v>827</v>
-      </c>
-      <c r="B54" s="36" t="s">
-        <v>959</v>
-      </c>
-      <c r="C54" s="36" t="s">
-        <v>805</v>
-      </c>
-      <c r="D54" s="36" t="s">
-        <v>889</v>
-      </c>
-      <c r="E54" s="36" t="s">
-        <v>942</v>
-      </c>
-      <c r="F54" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="36" t="s">
-        <v>828</v>
-      </c>
-      <c r="B55" s="36" t="s">
-        <v>960</v>
-      </c>
-      <c r="C55" s="36" t="s">
-        <v>805</v>
-      </c>
-      <c r="D55" s="36" t="s">
-        <v>895</v>
-      </c>
-      <c r="E55" s="36" t="s">
-        <v>893</v>
-      </c>
-      <c r="F55" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="36" t="s">
-        <v>829</v>
-      </c>
-      <c r="B56" s="36" t="s">
-        <v>961</v>
-      </c>
-      <c r="C56" s="36" t="s">
-        <v>805</v>
-      </c>
-      <c r="D56" s="36" t="s">
-        <v>889</v>
-      </c>
-      <c r="E56" s="36" t="s">
-        <v>962</v>
-      </c>
-      <c r="F56" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="36" t="s">
-        <v>830</v>
-      </c>
-      <c r="B57" s="36" t="s">
-        <v>916</v>
-      </c>
-      <c r="C57" s="36" t="s">
-        <v>805</v>
-      </c>
-      <c r="D57" s="36" t="s">
-        <v>895</v>
-      </c>
-      <c r="E57" s="36" t="s">
-        <v>917</v>
-      </c>
-      <c r="F57" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="36" t="s">
-        <v>831</v>
-      </c>
-      <c r="B58" s="36" t="s">
-        <v>963</v>
-      </c>
-      <c r="C58" s="36" t="s">
-        <v>805</v>
-      </c>
-      <c r="D58" s="36" t="s">
-        <v>889</v>
-      </c>
-      <c r="E58" s="36" t="s">
-        <v>799</v>
-      </c>
-      <c r="F58" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="36" t="s">
+      <c r="F59" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" s="36" t="s">
         <v>832</v>
       </c>
-      <c r="B59" s="36" t="s">
+      <c r="B60" s="36" t="s">
         <v>964</v>
       </c>
-      <c r="C59" s="36" t="s">
-        <v>805</v>
-      </c>
-      <c r="D59" s="36" t="s">
-        <v>895</v>
-      </c>
-      <c r="E59" s="36" t="s">
-        <v>801</v>
-      </c>
-      <c r="F59" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="36" t="s">
+      <c r="C60" s="36" t="s">
         <v>833</v>
       </c>
-      <c r="B60" s="36" t="s">
+      <c r="D60" s="36" t="s">
         <v>965</v>
-      </c>
-      <c r="C60" s="36" t="s">
-        <v>834</v>
-      </c>
-      <c r="D60" s="36" t="s">
-        <v>966</v>
       </c>
       <c r="E60" s="36" t="s">
         <v>387</v>
@@ -10847,18 +10844,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6">
       <c r="A61" s="36" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B61" s="36" t="s">
+        <v>966</v>
+      </c>
+      <c r="C61" s="36" t="s">
+        <v>833</v>
+      </c>
+      <c r="D61" s="36" t="s">
         <v>967</v>
-      </c>
-      <c r="C61" s="36" t="s">
-        <v>834</v>
-      </c>
-      <c r="D61" s="36" t="s">
-        <v>968</v>
       </c>
       <c r="E61" s="36" t="s">
         <v>387</v>
@@ -10867,821 +10864,821 @@
         <v>17</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6">
       <c r="A62" s="36" t="s">
+        <v>835</v>
+      </c>
+      <c r="B62" s="36" t="s">
+        <v>968</v>
+      </c>
+      <c r="C62" s="36" t="s">
+        <v>833</v>
+      </c>
+      <c r="D62" s="36" t="s">
+        <v>969</v>
+      </c>
+      <c r="E62" s="36" t="s">
+        <v>970</v>
+      </c>
+      <c r="F62" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" s="36" t="s">
         <v>836</v>
       </c>
-      <c r="B62" s="36" t="s">
-        <v>969</v>
-      </c>
-      <c r="C62" s="36" t="s">
-        <v>834</v>
-      </c>
-      <c r="D62" s="36" t="s">
-        <v>970</v>
-      </c>
-      <c r="E62" s="36" t="s">
+      <c r="B63" s="36" t="s">
         <v>971</v>
       </c>
-      <c r="F62" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="36" t="s">
+      <c r="C63" s="36" t="s">
+        <v>833</v>
+      </c>
+      <c r="D63" s="36" t="s">
+        <v>972</v>
+      </c>
+      <c r="E63" s="36" t="s">
+        <v>973</v>
+      </c>
+      <c r="F63" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" s="36" t="s">
+        <v>838</v>
+      </c>
+      <c r="B64" s="36" t="s">
+        <v>974</v>
+      </c>
+      <c r="C64" s="36" t="s">
+        <v>833</v>
+      </c>
+      <c r="D64" s="36" t="s">
+        <v>975</v>
+      </c>
+      <c r="E64" s="36" t="s">
+        <v>976</v>
+      </c>
+      <c r="F64" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" s="36" t="s">
+        <v>839</v>
+      </c>
+      <c r="B65" s="36" t="s">
+        <v>977</v>
+      </c>
+      <c r="C65" s="36" t="s">
+        <v>833</v>
+      </c>
+      <c r="D65" s="36" t="s">
+        <v>840</v>
+      </c>
+      <c r="E65" s="36" t="s">
+        <v>978</v>
+      </c>
+      <c r="F65" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" s="36" t="s">
+        <v>841</v>
+      </c>
+      <c r="B66" s="36" t="s">
+        <v>979</v>
+      </c>
+      <c r="C66" s="36" t="s">
+        <v>833</v>
+      </c>
+      <c r="D66" s="36" t="s">
+        <v>980</v>
+      </c>
+      <c r="E66" s="36" t="s">
+        <v>973</v>
+      </c>
+      <c r="F66" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="36" t="s">
+        <v>842</v>
+      </c>
+      <c r="B67" s="36" t="s">
+        <v>981</v>
+      </c>
+      <c r="C67" s="36" t="s">
+        <v>833</v>
+      </c>
+      <c r="D67" s="36" t="s">
+        <v>786</v>
+      </c>
+      <c r="E67" s="36" t="s">
+        <v>982</v>
+      </c>
+      <c r="F67" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" s="36" t="s">
+        <v>843</v>
+      </c>
+      <c r="B68" s="36" t="s">
+        <v>983</v>
+      </c>
+      <c r="C68" s="36" t="s">
+        <v>833</v>
+      </c>
+      <c r="D68" s="36" t="s">
+        <v>888</v>
+      </c>
+      <c r="E68" s="36" t="s">
+        <v>984</v>
+      </c>
+      <c r="F68" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69" s="36" t="s">
+        <v>844</v>
+      </c>
+      <c r="B69" s="36" t="s">
+        <v>985</v>
+      </c>
+      <c r="C69" s="36" t="s">
+        <v>833</v>
+      </c>
+      <c r="D69" s="36" t="s">
+        <v>894</v>
+      </c>
+      <c r="E69" s="36" t="s">
+        <v>892</v>
+      </c>
+      <c r="F69" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70" s="36" t="s">
+        <v>845</v>
+      </c>
+      <c r="B70" s="36" t="s">
+        <v>986</v>
+      </c>
+      <c r="C70" s="36" t="s">
+        <v>833</v>
+      </c>
+      <c r="D70" s="36" t="s">
+        <v>987</v>
+      </c>
+      <c r="E70" s="36" t="s">
+        <v>988</v>
+      </c>
+      <c r="F70" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" s="36" t="s">
+        <v>846</v>
+      </c>
+      <c r="B71" s="36" t="s">
+        <v>989</v>
+      </c>
+      <c r="C71" s="36" t="s">
+        <v>833</v>
+      </c>
+      <c r="D71" s="36" t="s">
+        <v>990</v>
+      </c>
+      <c r="E71" s="36" t="s">
+        <v>991</v>
+      </c>
+      <c r="F71" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72" s="36" t="s">
+        <v>847</v>
+      </c>
+      <c r="B72" s="36" t="s">
+        <v>992</v>
+      </c>
+      <c r="C72" s="36" t="s">
+        <v>833</v>
+      </c>
+      <c r="D72" s="36" t="s">
+        <v>993</v>
+      </c>
+      <c r="E72" s="36" t="s">
+        <v>994</v>
+      </c>
+      <c r="F72" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" s="36" t="s">
+        <v>848</v>
+      </c>
+      <c r="B73" s="36" t="s">
+        <v>995</v>
+      </c>
+      <c r="C73" s="36" t="s">
+        <v>833</v>
+      </c>
+      <c r="D73" s="36" t="s">
+        <v>996</v>
+      </c>
+      <c r="E73" s="36" t="s">
+        <v>800</v>
+      </c>
+      <c r="F73" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74" s="36" t="s">
+        <v>849</v>
+      </c>
+      <c r="B74" s="36" t="s">
+        <v>997</v>
+      </c>
+      <c r="C74" s="36" t="s">
+        <v>998</v>
+      </c>
+      <c r="D74" s="36" t="s">
+        <v>999</v>
+      </c>
+      <c r="E74" s="36" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F74" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75" s="36" t="s">
+        <v>850</v>
+      </c>
+      <c r="B75" s="36" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C75" s="36" t="s">
+        <v>998</v>
+      </c>
+      <c r="D75" s="36" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E75" s="36" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F75" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76" s="36" t="s">
+        <v>851</v>
+      </c>
+      <c r="B76" s="36" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C76" s="36" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D76" s="36" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E76" s="36" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F76" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77" s="36" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B77" s="36" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C77" s="36" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D77" s="36" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E77" s="36" t="s">
+        <v>1010</v>
+      </c>
+      <c r="F77" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78" s="36" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B78" s="36" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C78" s="36" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D78" s="36" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E78" s="36" t="s">
+        <v>1013</v>
+      </c>
+      <c r="F78" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" s="36" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B79" s="36" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C79" s="36" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D79" s="36" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E79" s="36" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F79" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" s="36" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B80" s="36" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C80" s="36" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D80" s="36" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E80" s="36" t="s">
+        <v>1019</v>
+      </c>
+      <c r="F80" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81" s="36" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B81" s="36" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C81" s="36" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D81" s="36" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E81" s="36" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F81" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82" s="36" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B82" s="36" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C82" s="36" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D82" s="36" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E82" s="36" t="s">
+        <v>798</v>
+      </c>
+      <c r="F82" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83" s="36" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B83" s="36" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C83" s="36" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D83" s="36" t="s">
         <v>837</v>
       </c>
-      <c r="B63" s="36" t="s">
-        <v>972</v>
-      </c>
-      <c r="C63" s="36" t="s">
-        <v>834</v>
-      </c>
-      <c r="D63" s="36" t="s">
-        <v>973</v>
-      </c>
-      <c r="E63" s="36" t="s">
-        <v>974</v>
-      </c>
-      <c r="F63" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="36" t="s">
-        <v>839</v>
-      </c>
-      <c r="B64" s="36" t="s">
-        <v>975</v>
-      </c>
-      <c r="C64" s="36" t="s">
-        <v>834</v>
-      </c>
-      <c r="D64" s="36" t="s">
-        <v>976</v>
-      </c>
-      <c r="E64" s="36" t="s">
-        <v>977</v>
-      </c>
-      <c r="F64" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="36" t="s">
-        <v>840</v>
-      </c>
-      <c r="B65" s="36" t="s">
-        <v>978</v>
-      </c>
-      <c r="C65" s="36" t="s">
-        <v>834</v>
-      </c>
-      <c r="D65" s="36" t="s">
-        <v>841</v>
-      </c>
-      <c r="E65" s="36" t="s">
-        <v>979</v>
-      </c>
-      <c r="F65" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="36" t="s">
-        <v>842</v>
-      </c>
-      <c r="B66" s="36" t="s">
-        <v>980</v>
-      </c>
-      <c r="C66" s="36" t="s">
-        <v>834</v>
-      </c>
-      <c r="D66" s="36" t="s">
-        <v>981</v>
-      </c>
-      <c r="E66" s="36" t="s">
-        <v>974</v>
-      </c>
-      <c r="F66" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="36" t="s">
-        <v>843</v>
-      </c>
-      <c r="B67" s="36" t="s">
-        <v>982</v>
-      </c>
-      <c r="C67" s="36" t="s">
-        <v>834</v>
-      </c>
-      <c r="D67" s="36" t="s">
-        <v>787</v>
-      </c>
-      <c r="E67" s="36" t="s">
-        <v>983</v>
-      </c>
-      <c r="F67" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="36" t="s">
-        <v>844</v>
-      </c>
-      <c r="B68" s="36" t="s">
-        <v>984</v>
-      </c>
-      <c r="C68" s="36" t="s">
-        <v>834</v>
-      </c>
-      <c r="D68" s="36" t="s">
-        <v>889</v>
-      </c>
-      <c r="E68" s="36" t="s">
-        <v>985</v>
-      </c>
-      <c r="F68" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="36" t="s">
-        <v>845</v>
-      </c>
-      <c r="B69" s="36" t="s">
-        <v>986</v>
-      </c>
-      <c r="C69" s="36" t="s">
-        <v>834</v>
-      </c>
-      <c r="D69" s="36" t="s">
-        <v>895</v>
-      </c>
-      <c r="E69" s="36" t="s">
-        <v>893</v>
-      </c>
-      <c r="F69" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="36" t="s">
-        <v>846</v>
-      </c>
-      <c r="B70" s="36" t="s">
-        <v>987</v>
-      </c>
-      <c r="C70" s="36" t="s">
-        <v>834</v>
-      </c>
-      <c r="D70" s="36" t="s">
-        <v>988</v>
-      </c>
-      <c r="E70" s="36" t="s">
-        <v>989</v>
-      </c>
-      <c r="F70" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="36" t="s">
-        <v>847</v>
-      </c>
-      <c r="B71" s="36" t="s">
-        <v>990</v>
-      </c>
-      <c r="C71" s="36" t="s">
-        <v>834</v>
-      </c>
-      <c r="D71" s="36" t="s">
-        <v>991</v>
-      </c>
-      <c r="E71" s="36" t="s">
-        <v>992</v>
-      </c>
-      <c r="F71" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="36" t="s">
-        <v>848</v>
-      </c>
-      <c r="B72" s="36" t="s">
-        <v>993</v>
-      </c>
-      <c r="C72" s="36" t="s">
-        <v>834</v>
-      </c>
-      <c r="D72" s="36" t="s">
-        <v>994</v>
-      </c>
-      <c r="E72" s="36" t="s">
-        <v>995</v>
-      </c>
-      <c r="F72" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="36" t="s">
-        <v>849</v>
-      </c>
-      <c r="B73" s="36" t="s">
-        <v>996</v>
-      </c>
-      <c r="C73" s="36" t="s">
-        <v>834</v>
-      </c>
-      <c r="D73" s="36" t="s">
-        <v>997</v>
-      </c>
-      <c r="E73" s="36" t="s">
-        <v>801</v>
-      </c>
-      <c r="F73" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="36" t="s">
-        <v>850</v>
-      </c>
-      <c r="B74" s="36" t="s">
-        <v>998</v>
-      </c>
-      <c r="C74" s="36" t="s">
-        <v>999</v>
-      </c>
-      <c r="D74" s="36" t="s">
-        <v>1000</v>
-      </c>
-      <c r="E74" s="36" t="s">
-        <v>1001</v>
-      </c>
-      <c r="F74" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="36" t="s">
-        <v>851</v>
-      </c>
-      <c r="B75" s="36" t="s">
-        <v>1002</v>
-      </c>
-      <c r="C75" s="36" t="s">
-        <v>999</v>
-      </c>
-      <c r="D75" s="36" t="s">
-        <v>1003</v>
-      </c>
-      <c r="E75" s="36" t="s">
-        <v>1004</v>
-      </c>
-      <c r="F75" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="36" t="s">
-        <v>852</v>
-      </c>
-      <c r="B76" s="36" t="s">
-        <v>1005</v>
-      </c>
-      <c r="C76" s="36" t="s">
-        <v>1006</v>
-      </c>
-      <c r="D76" s="36" t="s">
+      <c r="E83" s="36" t="s">
+        <v>800</v>
+      </c>
+      <c r="F83" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84" s="36" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B84" s="36" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C84" s="36" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D84" s="36" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E84" s="36" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F84" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" s="36" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B85" s="36" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C85" s="36" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D85" s="36" t="s">
+        <v>1037</v>
+      </c>
+      <c r="E85" s="36" t="s">
         <v>1007</v>
       </c>
-      <c r="E76" s="36" t="s">
-        <v>1008</v>
-      </c>
-      <c r="F76" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="36" t="s">
-        <v>1009</v>
-      </c>
-      <c r="B77" s="36" t="s">
-        <v>1099</v>
-      </c>
-      <c r="C77" s="36" t="s">
-        <v>1006</v>
-      </c>
-      <c r="D77" s="36" t="s">
+      <c r="F85" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86" s="36" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B86" s="36" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C86" s="36" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D86" s="36" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E86" s="36" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F86" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87" s="36" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B87" s="36" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C87" s="36" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D87" s="36" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E87" s="36" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F87" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88" s="36" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B88" s="36" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C88" s="36" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D88" s="36" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E88" s="36" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F88" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89" s="36" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B89" s="36" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C89" s="36" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D89" s="36" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E89" s="36" t="s">
+        <v>1048</v>
+      </c>
+      <c r="F89" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" s="36" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B90" s="36" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C90" s="36" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D90" s="36" t="s">
+        <v>1051</v>
+      </c>
+      <c r="E90" s="36" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F90" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91" s="36" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B91" s="36" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C91" s="36" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D91" s="36" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E91" s="36" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F91" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92" s="36" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B92" s="36" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C92" s="36" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D92" s="36" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E92" s="36" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F92" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93" s="36" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B93" s="36" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C93" s="36" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D93" s="36" t="s">
+        <v>1062</v>
+      </c>
+      <c r="E93" s="36" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F93" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94" s="36" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B94" s="36" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C94" s="36" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D94" s="36" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E94" s="36" t="s">
+        <v>1065</v>
+      </c>
+      <c r="F94" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95" s="36" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B95" s="36" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C95" s="36" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D95" s="36" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E95" s="36" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F95" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" s="36" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B96" s="36" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C96" s="36" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D96" s="36" t="s">
+        <v>1071</v>
+      </c>
+      <c r="E96" s="36" t="s">
+        <v>1072</v>
+      </c>
+      <c r="F96" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97" s="36" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B97" s="36" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C97" s="36" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D97" s="36" t="s">
+        <v>1074</v>
+      </c>
+      <c r="E97" s="36" t="s">
+        <v>1072</v>
+      </c>
+      <c r="F97" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98" s="36" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B98" s="36" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C98" s="36" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D98" s="36" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E98" s="36" t="s">
+        <v>1077</v>
+      </c>
+      <c r="F98" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99" s="36" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B99" s="36" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C99" s="36" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D99" s="36" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E99" s="36" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F99" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100" s="36" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B100" s="36" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C100" s="36" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D100" s="36" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E100" s="36" t="s">
         <v>1010</v>
       </c>
-      <c r="E77" s="36" t="s">
-        <v>1011</v>
-      </c>
-      <c r="F77" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="36" t="s">
+      <c r="F100" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101" s="36" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B101" s="36" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C101" s="36" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D101" s="36" t="s">
         <v>1012</v>
       </c>
-      <c r="B78" s="36" t="s">
-        <v>1091</v>
-      </c>
-      <c r="C78" s="36" t="s">
-        <v>1006</v>
-      </c>
-      <c r="D78" s="36" t="s">
-        <v>1013</v>
-      </c>
-      <c r="E78" s="36" t="s">
-        <v>1014</v>
-      </c>
-      <c r="F78" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="36" t="s">
-        <v>1015</v>
-      </c>
-      <c r="B79" s="36" t="s">
-        <v>1106</v>
-      </c>
-      <c r="C79" s="36" t="s">
-        <v>1006</v>
-      </c>
-      <c r="D79" s="36" t="s">
-        <v>1016</v>
-      </c>
-      <c r="E79" s="36" t="s">
-        <v>1017</v>
-      </c>
-      <c r="F79" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="36" t="s">
-        <v>1018</v>
-      </c>
-      <c r="B80" s="36" t="s">
-        <v>1100</v>
-      </c>
-      <c r="C80" s="36" t="s">
-        <v>1006</v>
-      </c>
-      <c r="D80" s="36" t="s">
-        <v>1019</v>
-      </c>
-      <c r="E80" s="36" t="s">
-        <v>1020</v>
-      </c>
-      <c r="F80" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="36" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B81" s="36" t="s">
-        <v>1022</v>
-      </c>
-      <c r="C81" s="36" t="s">
-        <v>1023</v>
-      </c>
-      <c r="D81" s="36" t="s">
-        <v>1024</v>
-      </c>
-      <c r="E81" s="36" t="s">
-        <v>1025</v>
-      </c>
-      <c r="F81" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="36" t="s">
-        <v>1026</v>
-      </c>
-      <c r="B82" s="36" t="s">
-        <v>1027</v>
-      </c>
-      <c r="C82" s="36" t="s">
-        <v>1023</v>
-      </c>
-      <c r="D82" s="36" t="s">
-        <v>1028</v>
-      </c>
-      <c r="E82" s="36" t="s">
-        <v>799</v>
-      </c>
-      <c r="F82" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="36" t="s">
-        <v>1029</v>
-      </c>
-      <c r="B83" s="36" t="s">
-        <v>1030</v>
-      </c>
-      <c r="C83" s="36" t="s">
-        <v>1023</v>
-      </c>
-      <c r="D83" s="36" t="s">
-        <v>838</v>
-      </c>
-      <c r="E83" s="36" t="s">
-        <v>801</v>
-      </c>
-      <c r="F83" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="36" t="s">
-        <v>1031</v>
-      </c>
-      <c r="B84" s="36" t="s">
-        <v>1032</v>
-      </c>
-      <c r="C84" s="36" t="s">
-        <v>1023</v>
-      </c>
-      <c r="D84" s="36" t="s">
-        <v>1033</v>
-      </c>
-      <c r="E84" s="36" t="s">
-        <v>1034</v>
-      </c>
-      <c r="F84" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="36" t="s">
-        <v>1035</v>
-      </c>
-      <c r="B85" s="36" t="s">
-        <v>1036</v>
-      </c>
-      <c r="C85" s="36" t="s">
-        <v>1037</v>
-      </c>
-      <c r="D85" s="36" t="s">
-        <v>1038</v>
-      </c>
-      <c r="E85" s="36" t="s">
-        <v>1008</v>
-      </c>
-      <c r="F85" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="36" t="s">
-        <v>1039</v>
-      </c>
-      <c r="B86" s="36" t="s">
-        <v>1092</v>
-      </c>
-      <c r="C86" s="36" t="s">
-        <v>1037</v>
-      </c>
-      <c r="D86" s="36" t="s">
-        <v>1013</v>
-      </c>
-      <c r="E86" s="36" t="s">
-        <v>1040</v>
-      </c>
-      <c r="F86" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="36" t="s">
-        <v>1041</v>
-      </c>
-      <c r="B87" s="36" t="s">
-        <v>1105</v>
-      </c>
-      <c r="C87" s="36" t="s">
-        <v>1037</v>
-      </c>
-      <c r="D87" s="36" t="s">
-        <v>1042</v>
-      </c>
-      <c r="E87" s="36" t="s">
-        <v>1040</v>
-      </c>
-      <c r="F87" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="36" t="s">
-        <v>1043</v>
-      </c>
-      <c r="B88" s="36" t="s">
-        <v>1093</v>
-      </c>
-      <c r="C88" s="36" t="s">
-        <v>1037</v>
-      </c>
-      <c r="D88" s="36" t="s">
-        <v>1044</v>
-      </c>
-      <c r="E88" s="36" t="s">
-        <v>1040</v>
-      </c>
-      <c r="F88" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="36" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B89" s="36" t="s">
-        <v>1046</v>
-      </c>
-      <c r="C89" s="36" t="s">
-        <v>1047</v>
-      </c>
-      <c r="D89" s="36" t="s">
-        <v>1048</v>
-      </c>
-      <c r="E89" s="36" t="s">
-        <v>1049</v>
-      </c>
-      <c r="F89" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="36" t="s">
-        <v>1050</v>
-      </c>
-      <c r="B90" s="36" t="s">
-        <v>1051</v>
-      </c>
-      <c r="C90" s="36" t="s">
-        <v>1047</v>
-      </c>
-      <c r="D90" s="36" t="s">
-        <v>1052</v>
-      </c>
-      <c r="E90" s="36" t="s">
-        <v>1053</v>
-      </c>
-      <c r="F90" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="36" t="s">
-        <v>1054</v>
-      </c>
-      <c r="B91" s="36" t="s">
-        <v>1055</v>
-      </c>
-      <c r="C91" s="36" t="s">
-        <v>1056</v>
-      </c>
-      <c r="D91" s="36" t="s">
-        <v>1057</v>
-      </c>
-      <c r="E91" s="36" t="s">
-        <v>1008</v>
-      </c>
-      <c r="F91" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="36" t="s">
-        <v>1058</v>
-      </c>
-      <c r="B92" s="36" t="s">
-        <v>1101</v>
-      </c>
-      <c r="C92" s="36" t="s">
-        <v>1056</v>
-      </c>
-      <c r="D92" s="36" t="s">
-        <v>1059</v>
-      </c>
-      <c r="E92" s="36" t="s">
-        <v>1060</v>
-      </c>
-      <c r="F92" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="36" t="s">
-        <v>1061</v>
-      </c>
-      <c r="B93" s="36" t="s">
-        <v>1062</v>
-      </c>
-      <c r="C93" s="36" t="s">
-        <v>1056</v>
-      </c>
-      <c r="D93" s="36" t="s">
-        <v>1063</v>
-      </c>
-      <c r="E93" s="36" t="s">
-        <v>1008</v>
-      </c>
-      <c r="F93" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="36" t="s">
-        <v>1064</v>
-      </c>
-      <c r="B94" s="36" t="s">
-        <v>1094</v>
-      </c>
-      <c r="C94" s="36" t="s">
-        <v>1056</v>
-      </c>
-      <c r="D94" s="36" t="s">
-        <v>1065</v>
-      </c>
-      <c r="E94" s="36" t="s">
-        <v>1066</v>
-      </c>
-      <c r="F94" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="36" t="s">
-        <v>1067</v>
-      </c>
-      <c r="B95" s="36" t="s">
-        <v>1068</v>
-      </c>
-      <c r="C95" s="36" t="s">
-        <v>1069</v>
-      </c>
-      <c r="D95" s="36" t="s">
-        <v>1070</v>
-      </c>
-      <c r="E95" s="36" t="s">
-        <v>1008</v>
-      </c>
-      <c r="F95" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" s="36" t="s">
-        <v>1071</v>
-      </c>
-      <c r="B96" s="36" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C96" s="36" t="s">
-        <v>1069</v>
-      </c>
-      <c r="D96" s="36" t="s">
-        <v>1072</v>
-      </c>
-      <c r="E96" s="36" t="s">
-        <v>1073</v>
-      </c>
-      <c r="F96" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A97" s="36" t="s">
-        <v>1074</v>
-      </c>
-      <c r="B97" s="36" t="s">
-        <v>1095</v>
-      </c>
-      <c r="C97" s="36" t="s">
-        <v>1069</v>
-      </c>
-      <c r="D97" s="36" t="s">
-        <v>1075</v>
-      </c>
-      <c r="E97" s="36" t="s">
-        <v>1073</v>
-      </c>
-      <c r="F97" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A98" s="36" t="s">
-        <v>1076</v>
-      </c>
-      <c r="B98" s="36" t="s">
-        <v>1096</v>
-      </c>
-      <c r="C98" s="36" t="s">
-        <v>1069</v>
-      </c>
-      <c r="D98" s="36" t="s">
-        <v>1077</v>
-      </c>
-      <c r="E98" s="36" t="s">
-        <v>1078</v>
-      </c>
-      <c r="F98" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A99" s="36" t="s">
-        <v>1079</v>
-      </c>
-      <c r="B99" s="36" t="s">
+      <c r="E101" s="36" t="s">
+        <v>1085</v>
+      </c>
+      <c r="F101" s="36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102" s="36" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B102" s="36" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C102" s="36" t="s">
         <v>1080</v>
       </c>
-      <c r="C99" s="36" t="s">
-        <v>1081</v>
-      </c>
-      <c r="D99" s="36" t="s">
-        <v>1082</v>
-      </c>
-      <c r="E99" s="36" t="s">
-        <v>1008</v>
-      </c>
-      <c r="F99" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A100" s="36" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B100" s="36" t="s">
-        <v>1103</v>
-      </c>
-      <c r="C100" s="36" t="s">
-        <v>1081</v>
-      </c>
-      <c r="D100" s="36" t="s">
-        <v>1084</v>
-      </c>
-      <c r="E100" s="36" t="s">
-        <v>1011</v>
-      </c>
-      <c r="F100" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A101" s="36" t="s">
-        <v>1085</v>
-      </c>
-      <c r="B101" s="36" t="s">
-        <v>1097</v>
-      </c>
-      <c r="C101" s="36" t="s">
-        <v>1081</v>
-      </c>
-      <c r="D101" s="36" t="s">
-        <v>1013</v>
-      </c>
-      <c r="E101" s="36" t="s">
-        <v>1086</v>
-      </c>
-      <c r="F101" s="36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A102" s="36" t="s">
+      <c r="D102" s="36" t="s">
         <v>1087</v>
       </c>
-      <c r="B102" s="36" t="s">
-        <v>1104</v>
-      </c>
-      <c r="C102" s="36" t="s">
-        <v>1081</v>
-      </c>
-      <c r="D102" s="36" t="s">
+      <c r="E102" s="36" t="s">
         <v>1088</v>
-      </c>
-      <c r="E102" s="36" t="s">
-        <v>1089</v>
       </c>
       <c r="F102" s="36" t="s">
         <v>17</v>
@@ -11696,11 +11693,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87B45724-6105-477F-BAA9-89F087DA624C}">
   <dimension ref="B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:2">
       <c r="B2" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
   </sheetData>
